--- a/data_extactor/batch/901_950.xlsx
+++ b/data_extactor/batch/901_950.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E17B4F-6C06-4668-B2CD-03398DA48EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1627 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="538">
+  <si>
+    <t>51-8021.00</t>
+  </si>
+  <si>
+    <t>Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Auxiliary Operator | Boiler Operator | Boiler Technician (Boiler Tech) | Operating Engineer | Operator | Plant Utilities Engineer | Recovery Boiler Operator | Stationary Engineer | Stationary Steam Engineer | Utilities Operator</t>
+  </si>
+  <si>
+    <t>Building management system software | Computerized maintenance management system CMMS | Database software | Email software | Graphics software | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational Data Store ODS software | SAP software | Statistical software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Active Learning | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Chemistry | Public Safety and Security | Physics | Engineering and Technology | English Language | Computers and Electronics | Mathematics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Oral Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Perceptual Speed | Auditory Attention | Reaction Time | Multilimb Coordination | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Category Flexibility | Written Comprehension | Speech Clarity | Speech Recognition | Far Vision | Written Expression</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | E-Mail | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Exposed to Hazardous Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Consequence of Error | Work Outcomes and Results of Other Workers | Exposed to Hazardous Equipment | Frequency of Decision Making | Importance of Repeating Same Tasks | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Time Pressure | Exposed to High Places | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Boilermakers | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Engine and Other Machine Assemblers | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Technicians | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Hydroelectric Plant Technicians | Industrial Machinery Mechanics | Maintenance and Repair Workers, General | Mechanical Engineers | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Plumbers, Pipefitters, and Steamfitters | Power Distributors and Dispatchers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Ship Engineers | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Operate or maintain stationary engines, boilers, or other mechanical equipment to provide utilities for buildings or industrial processes. Operate equipment such as steam engines, generators, motors, turbines, and steam boilers.</t>
+  </si>
+  <si>
+    <t>Activate valves to maintain required amounts of water in boilers, to adjust supplies of combustion air, and to control the flow of fuel into burners. | Adjust controls and/or valves on equipment to provide power, and to regulate and set operations of system or industrial processes. | Analyze problems and take appropriate action to ensure continuous and reliable operation of equipment and systems. | Check the air quality of ventilation systems and make adjustments to ensure compliance with mandated safety codes. | Clean and lubricate boilers and auxiliary equipment and make minor adjustments as needed, using hand tools. | Contact equipment manufacturers or appropriate specialists when necessary to resolve equipment problems. | Develop operation, safety, and maintenance procedures or assist in their development. | Fire coal furnaces by hand or with stokers and gas- or oil-fed boilers, using automatic gas feeds or oil pumps. | Ignite fuel in burners, using torches or flames. | Install burners and auxiliary equipment, using hand tools. | Investigate and report on accidents. | Maintain daily logs of operation, maintenance, and safety activities, including test results, instrument readings, and details of equipment malfunctions and maintenance work. | Monitor and inspect equipment, computer terminals, switches, valves, gauges, alarms, safety devices, and meters to detect leaks or malfunctions and to ensure that equipment is operating efficiently and safely. | Monitor boiler water, chemical, and fuel levels, and make adjustments to maintain required levels. | Observe and interpret readings on gauges, meters, and charts registering various aspects of boiler operation to ensure that boilers are operating properly. | Operate mechanical hoppers and provide assistance in their adjustment and repair. | Operate or tend stationary engines, boilers, and auxiliary equipment, such as pumps, compressors, or air-conditioning equipment, to supply and maintain steam or heat for buildings, marine vessels, or pneumatic tools. | Perform or arrange for repairs, such as complete overhauls, replacement of defective valves, gaskets, or bearings, or fabrication of new parts. | Provide assistance to plumbers in repairing or replacing water, sewer, or waste lines, and in daily maintenance activities. | Receive instructions from steam engineers regarding steam plant and air compressor operations. | Supervise the work of assistant stationary engineers, turbine operators, boiler tenders, or air conditioning and refrigeration operators and mechanics. | Switch from automatic to manual controls and isolate equipment mechanically and electrically to allow for safe inspection and repair work. | Test boiler water quality or arrange for testing and take necessary corrective action, such as adding chemicals to prevent corrosion and harmful deposits. | Test electrical systems to determine voltages, using voltage meters. | Weigh, measure, and record fuel used.</t>
+  </si>
+  <si>
+    <t>51-8031.00</t>
+  </si>
+  <si>
+    <t>Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Plant Operator | Process Operator (Process Op) | Relief Operator | Waste Water Treatment Plant Operator (WWTP Operator) | Wastewater Operator (WW Operator) | Wastewater Technician (Wastewater Tech) | Water Control Dispatcher | Water Plant Operator | Water Treatment Operator | Water Treatment Plant Operator</t>
+  </si>
+  <si>
+    <t>Data logging software | Database software | Geographic information system GIS systems | Human machine interface HMI software | Material safety data sheet MSDS software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational Data Store ODS software | Records management software | Supervisory control and data acquisition SCADA software | Timekeeping software | Wastewater expert control systems</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Mechanical | English Language | Chemistry | Mathematics | Administration and Management | Education and Training | Customer and Personal Service | Computers and Electronics | Law and Government | Engineering and Technology | Biology | Administrative | Production and Processing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Deductive Reasoning | Written Comprehension | Control Precision | Selective Attention | Information Ordering | Inductive Reasoning | Problem Sensitivity | Written Expression | Trunk Strength | Manual Dexterity | Arm-Hand Steadiness | Perceptual Speed | Flexibility of Closure | Speech Clarity | Speech Recognition | Far Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Environmentally Controlled | Exposed to Hazardous Conditions | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Contact With Others | Time Pressure | Determine Tasks, Priorities and Goals | Outdoors, Under Cover | Exposed to Hazardous Equipment | Frequency of Decision Making | Importance of Repeating Same Tasks | Consequence of Error | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Exposed to Very Hot or Cold Temperatures | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Environmental Science and Protection Technicians, Including Health | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hazardous Materials Removal Workers | Hydroelectric Plant Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Recycling and Reclamation Workers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Septic Tank Servicers and Sewer Pipe Cleaners | Stationary Engineers and Boiler Operators | Water/Wastewater Engineers</t>
+  </si>
+  <si>
+    <t>Operate or control an entire process or system of machines, often through the use of control boards, to transfer or treat water or wastewater.</t>
+  </si>
+  <si>
+    <t>Add chemicals, such as ammonia, chlorine, or lime, to disinfect and deodorize water and other liquids. | Clean and maintain tanks, filter beds, and other work areas, using hand tools and power tools. | Collect and test water and sewage samples, using test equipment and color analysis standards. | Direct and coordinate plant workers engaged in routine operations and maintenance activities. | Inspect equipment or monitor operating conditions, meters, and gauges to determine load requirements and detect malfunctions. | Maintain, repair, and lubricate equipment, using hand tools and power tools. | Operate and adjust controls on equipment to purify and clarify water, process or dispose of sewage, and generate power. | Record operational data, personnel attendance, or meter and gauge readings on specified forms.</t>
+  </si>
+  <si>
+    <t>51-8091.00</t>
+  </si>
+  <si>
+    <t>Chemical Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Chemical Operator | Loader Technician | Process Control Operator | Process Development Associate | Process Operator | Process Technician | Production Technician</t>
+  </si>
+  <si>
+    <t>Alarm management system software | Coordinated incident management system CIMS software | Distributed control system DCS | Interlock shutdown systems | Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Active Learning | Reading Comprehension | Speaking | Writing</t>
+  </si>
+  <si>
+    <t>Production and Processing | Chemistry | Mechanical | English Language | Public Safety and Security | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Selective Attention | Near Vision | Oral Expression | Deductive Reasoning | Oral Comprehension | Far Vision | Control Precision | Perceptual Speed | Information Ordering | Hearing Sensitivity | Arm-Hand Steadiness | Written Comprehension | Reaction Time | Auditory Attention | Speech Clarity | Speech Recognition | Visual Color Discrimination | Manual Dexterity | Flexibility of Closure | Inductive Reasoning | Written Expression | Finger Dexterity | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Frequency of Decision Making | Telephone Conversations | Indoors, Environmentally Controlled | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Pace Determined by Speed of Equipment | Contact With Others | Freedom to Make Decisions | Outdoors, Under Cover | Consequence of Error | Time Pressure | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to High Places | Exposed to Hazardous Equipment | Degree of Automation | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Physical Proximity | E-Mail</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Chemical Engineers | Chemical Equipment Operators and Tenders | Chemical Technicians | Chemists | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Metal-Refining Furnace Operators and Tenders | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Semiconductor Processing Technicians | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Control or operate entire chemical processes or system of machines.</t>
+  </si>
+  <si>
+    <t>Calculate material requirements or yields according to formulas. | Confer with technical and supervisory personnel to report or resolve conditions affecting safety, efficiency, or product quality. | Control or operate chemical processes or systems of machines, using panelboards, control boards, or semi-automatic equipment. | Defrost frozen valves, using steam hoses. | Direct workers engaged in operating machinery that regulates the flow of materials and products. | Draw samples of products and conduct quality control tests to monitor processing and to ensure that standards are met. | Gauge tank levels, using calibrated rods. | Inspect operating units, such as towers, soap-spray storage tanks, scrubbers, collectors, or driers to ensure that all are functioning and to maintain maximum efficiency. | Interpret chemical reactions visible through sight glasses or on television monitors and review laboratory test reports for process adjustments. | Monitor recording instruments, flowmeters, panel lights, or other indicators and listen for warning signals to verify conformity of process conditions. | Move control settings to make necessary adjustments on equipment units affecting speeds of chemical reactions, quality, or yields. | Notify maintenance, stationary engineering, or other auxiliary personnel to correct equipment malfunctions or to adjust power, steam, water, or air supplies. | Patrol work areas to ensure that solutions in tanks or troughs are not in danger of overflowing. | Record operating data, such as process conditions, test results, or instrument readings. | Regulate or shut down equipment during emergency situations, as directed by supervisory personnel. | Repair or replace damaged equipment. | Start pumps to wash and rinse reactor vessels, to exhaust gases or vapors, to regulate the flow of oil, steam, air, or perfume to towers, or to add products to converter or blending vessels. | Supervise the cleaning of towers, strainers, or spray tips. | Turn valves to regulate flow of products or byproducts through agitator tanks, storage drums, or neutralizer tanks.</t>
+  </si>
+  <si>
+    <t>51-8092.00</t>
+  </si>
+  <si>
+    <t>Gas Plant Operators</t>
+  </si>
+  <si>
+    <t>Compressor Technician (Compressor Tech) | Engine Room Operator | Gas Controller | Gas Dispatcher | Gas Plant Operator | Gas Resource Control Operator | Gas System Operator | Liquefied Natural Gas Technician (LNG Technician) | Liquid Natural Gas Plant Operator (LNG Plant Operator) | Plant Operator</t>
+  </si>
+  <si>
+    <t>AspenTech HYSYS | Google Android | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operating log software | Quorum PGAS | SAP software | Supervisory control and data acquisition SCADA software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Reading Comprehension | Speaking | Writing | Active Listening</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Mechanical | English Language | Computers and Electronics | Mathematics | Engineering and Technology | Production and Processing | Customer and Personal Service | Administrative</t>
+  </si>
+  <si>
+    <t>Perceptual Speed | Near Vision | Problem Sensitivity | Auditory Attention | Selective Attention | Oral Comprehension | Deductive Reasoning | Flexibility of Closure | Far Vision | Reaction Time | Information Ordering | Written Expression | Written Comprehension | Time Sharing | Visualization | Category Flexibility | Inductive Reasoning | Oral Expression | Speech Clarity | Speech Recognition | Hearing Sensitivity | Visual Color Discrimination | Rate Control | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Health and Safety of Other Workers | Freedom to Make Decisions | Contact With Others | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Exposed to Hazardous Conditions | Exposed to Contaminants | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Very Hot or Cold Temperatures | Time Pressure</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Biomass Power Plant Managers | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Control and Valve Installers and Repairers, Except Mechanical Door | Gas Compressor and Gas Pumping Station Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Distributors and Dispatchers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Service Unit Operators, Oil and Gas | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Distribute or process gas for utility companies and others by controlling compressors to maintain specified pressures on main pipelines.</t>
+  </si>
+  <si>
+    <t>Adjust temperature, pressure, vacuum, level, flow rate, or transfer of gas to maintain processes at required levels or to correct problems. | Calculate gas ratios to detect deviations from specifications, using testing apparatus. | Change charts in recording meters. | Clean, maintain, and repair equipment, using hand tools, or request that repair and maintenance work be performed. | Collaborate with other operators to solve unit problems. | Contact maintenance crews when necessary. | Control equipment to regulate flow and pressure of gas to feedlines of boilers, furnaces, and related steam-generating or heating equipment. | Control fractioning columns, compressors, purifying towers, heat exchangers, and related equipment to extract nitrogen and oxygen from air. | Control operation of compressors, scrubbers, evaporators, and refrigeration equipment to liquefy, compress, or regasify natural gas. | Determine causes of abnormal pressure variances, and make corrective recommendations, such as installation of pipes to relieve overloading. | Distribute or process gas for utility companies or industrial plants, using panel boards, control boards, and semi-automatic equipment. | Monitor equipment functioning, observe temperature, level, and flow gauges, and perform regular unit checks to ensure that all equipment is operating as it should. | Monitor transportation and storage of flammable and other potentially dangerous products to ensure that safety guidelines are followed. | Operate construction equipment to install and maintain gas distribution systems. | Read logsheets to determine product demand and disposition, or to detect malfunctions. | Record, review, and compile operations records, test results, and gauge readings such as temperatures, pressures, concentrations, and flows. | Signal or direct workers who tend auxiliary equipment. | Start and shut down plant equipment. | Test gas, chemicals, and air during processing to assess factors such as purity and moisture content, and to detect quality problems or gas or chemical leaks.</t>
+  </si>
+  <si>
+    <t>51-8093.00</t>
+  </si>
+  <si>
+    <t>Petroleum Pump System Operators, Refinery Operators, and Gaugers</t>
+  </si>
+  <si>
+    <t>Board Operator | Crude Unit Operator | Gauger | Hydrotreater Operator | Operator | Outside Operator | Pumper | Refinery Operator | Stillman | Unit Operator</t>
+  </si>
+  <si>
+    <t>Email software | Inventory tracking software | Microsoft Excel | Microsoft Outlook | Microsoft Word | Programmable logic controller PLC software | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Speaking | Active Learning | Critical Thinking | Writing | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Public Safety and Security | Mechanical | Administration and Management | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Information Ordering | Flexibility of Closure | Perceptual Speed | Near Vision | Problem Sensitivity | Selective Attention | Auditory Attention | Hearing Sensitivity | Deductive Reasoning | Speech Recognition | Control Precision | Category Flexibility | Inductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Visualization | Written Expression | Visual Color Discrimination | Far Vision | Reaction Time | Multilimb Coordination | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Conditions | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Telephone Conversations | Exposed to High Places | Contact With Others | Consequence of Error | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Health and Safety of Other Workers | E-Mail | Outdoors, Under Cover | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Environmentally Controlled | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Repeating Same Tasks | Time Pressure | Freedom to Make Decisions | Exposed to Hazardous Equipment | Written Letters and Memos | Work Outcomes and Results of Other Workers | Indoors, Not Environmentally Controlled | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Biomass Power Plant Managers | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Control and Valve Installers and Repairers, Except Mechanical Door | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Technicians | Hydroelectric Plant Technicians | Petroleum Engineers | Power Distributors and Dispatchers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Rotary Drill Operators, Oil and Gas | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Service Unit Operators, Oil and Gas | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Operate or control petroleum refining or processing units. May specialize in controlling manifold and pumping systems, gauging or testing oil in storage tanks, or regulating the flow of oil into pipelines.</t>
+  </si>
+  <si>
+    <t>Calculate test result values, using standard formulas. | Clamp seals around valves to secure tanks. | Clean interiors of processing units by circulating chemicals and solvents within units. | Collect product samples by turning bleeder valves, or by lowering containers into tanks to obtain oil samples. | Conduct general housekeeping of units, including wiping up oil spills and performing general cleaning duties. | Control or operate manifold and pumping systems to circulate liquids through a petroleum refinery. | Coordinate shutdowns and major projects. | Inspect pipelines, tightening connections and lubricating valves as necessary. | Lower thermometers into tanks to obtain temperature readings. | Maintain and repair equipment, or report malfunctioning equipment to supervisors so that repairs can be scheduled. | Monitor process indicators, instruments, gauges, and meters to detect and report any possible problems. | Operate auxiliary equipment and control multiple processing units during distilling or treating operations, moving controls that regulate valves, pumps, compressors, and auxiliary equipment. | Operate control panels to coordinate and regulate process variables such as temperature and pressure, and to direct product flow rate, according to process schedules. | Patrol units to monitor the amount of oil in storage tanks, and to verify that activities and operations are safe, efficient, and in compliance with regulations. | Perform tests to check the qualities and grades of products, such as assessing levels of bottom sediment, water, and foreign materials in oil samples, using centrifugal testers. | Plan movement of products through lines to processing, storage, and shipping units, using knowledge of system interconnections and capacities. | Prepare calculations for receipts and deliveries of oil and oil products. | Read and analyze specifications, schedules, logs, test results, and laboratory recommendations to determine how to set equipment controls to produce the required qualities and quantities of products. | Read automatic gauges at specified intervals to determine the flow rate of oil into or from tanks, and the amount of oil in tanks. | Record and compile operating data, instrument readings, documentation, and results of laboratory analyses. | Signal other workers by telephone or radio to operate pumps, open and close valves, and check temperatures. | Start pumps and open valves or use automated equipment to regulate the flow of oil in pipelines and into and out of tanks. | Synchronize activities with other pumphouses to ensure a continuous flow of products and a minimum of contamination between products. | Verify that incoming and outgoing products are moving through the correct meters, and that meters are working properly.</t>
+  </si>
+  <si>
+    <t>51-8099.00</t>
+  </si>
+  <si>
+    <t>Plant and System Operators, All Other</t>
+  </si>
+  <si>
+    <t>Boiler Operator | Compressor Operator | Control Room Operator | Plant Operator | Process Operator | Systems Operator | Utility Operator | Facility Systems Operator | Steam Plant Operator | Refrigeration Plant Operator</t>
+  </si>
+  <si>
+    <t>Supervisory control and data acquisition SCADA software | Programmable logic controller PLC software | Statistical process control SPC software | Materials requirement planning MRP software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Enterprise resource planning ERP system | Database software | SAP software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Physics | Chemistry | Computers and Electronics | English Language | Mathematics | Public Safety and Security | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision | Auditory Attention | Reaction Time</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Power Plant Operators | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Chemical Plant and System Operators | Gas Plant Operators | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Nuclear Power Reactor Operators | Power Distributors and Dispatchers | Biomass Plant Technicians | Hydroelectric Plant Technicians | Biofuels Processing Technicians | Chemical Equipment Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Pump Operators, Except Wellhead Pumpers | Industrial Machinery Mechanics | Maintenance and Repair Workers, General | First-Line Supervisors of Production and Operating Workers | Control and Valve Installers and Repairers, Except Mechanical Door | Occupational Health and Safety Technicians | Production Workers, All Other</t>
+  </si>
+  <si>
+    <t>All plant and system operators not listed separately.</t>
+  </si>
+  <si>
+    <t>Operate and control plant systems in roles not classified separately. | Monitor gauges, meters, control panels, and computer displays. | Adjust valves, controls, and equipment to regulate process conditions. | Start up, shut down, and switch over equipment according to procedures. | Record operating data such as temperatures, pressures, flows, and levels. | Detect abnormal conditions and take corrective action or notify supervisors. | Perform routine inspections, lubrication, and preventive maintenance. | Collect samples and perform basic tests to verify process quality. | Follow lockout, confined space, and hazardous energy procedures. | Coordinate with maintenance crews during repairs and outages. | Maintain logs, shift reports, and regulatory compliance records. | Respond to alarms, emergencies, and equipment failures. | Clean equipment, work areas, and remove waste materials. | Train and direct assistant operators and helpers.</t>
+  </si>
+  <si>
+    <t>51-8099.01</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technician | Board Operator | Chemical Operator | Ethanol Operator | Mash Preparatory Operator | Process Operator | Process Technician | Production Operator</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Data visualization software | Digital control systems DCS | Human machine interface HMI software | Inventory control software | Microsoft Excel | Microsoft Word | Python | R | SAS | Tableau</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Speaking | Active Listening | Writing | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | English Language | Public Safety and Security | Chemistry | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Control Precision | Speech Recognition | Oral Comprehension | Oral Expression | Written Comprehension | Arm-Hand Steadiness | Selective Attention | Perceptual Speed | Information Ordering | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Reaction Time | Manual Dexterity | Speech Clarity | Visual Color Discrimination | Near Vision | Finger Dexterity | Multilimb Coordination | Written Expression | Auditory Attention | Rate Control | Time Sharing | Flexibility of Closure | Category Flexibility | Visualization | Far Vision | Extent Flexibility | Trunk Strength | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Hazardous Conditions | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Pace Determined by Speed of Equipment | Outdoors, Exposed to All Weather Conditions | Freedom to Make Decisions | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Determine Tasks, Priorities and Goals | Exposed to High Places | Consequence of Error | Time Pressure | Importance of Repeating Same Tasks | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | In an Open Vehicle or Operating Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Outdoors, Under Cover | Degree of Automation</t>
+  </si>
+  <si>
+    <t>Agricultural Technicians | Biofuels Production Managers | Biofuels/Biodiesel Technology and Product Development Managers | Biomass Plant Technicians | Biomass Power Plant Managers | Chemical Engineers | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Industrial Engineering Technologists and Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Calculate, measure, load, mix, and process refined feedstock with additives in fermentation or reaction process vessels and monitor production process. Perform, and keep records of, plant maintenance, repairs, and safety inspections.</t>
+  </si>
+  <si>
+    <t>Assess the quality of biofuels additives for reprocessing. | Calculate, measure, load, or mix refined feedstock used in biofuels production. | Calibrate liquid flow devices and meters, including fuel, chemical, and water meters. | Clean biofuels processing work area, ensuring compliance with safety regulations. | Collect biofuels samples and perform routine laboratory tests or analyses to assess biofuels quality. | Coordinate raw product sourcing or collection. | Inspect biofuels plant or processing equipment regularly, recording or reporting damage and mechanical problems. | Measure and monitor raw biofuels feedstock. | Monitor and record biofuels processing data. | Monitor and record flow meter performance. | Monitor batch, continuous flow, or hybrid biofuels production processes. | Monitor stored biofuels products or secondary by-products until reused or transferred to users. | Operate chemical processing equipment for the production of biofuels. | Operate equipment, such as a centrifuge, to extract biofuels products and secondary by-products or reusable fractions. | Operate valves, pumps, engines, or generators to control and adjust biofuels production. | Perform routine maintenance on mechanical, electrical, or electronic equipment or instruments used in the processing of biofuels. | Preprocess feedstock in preparation for physical, chemical, or biological fuel production processes. | Process refined feedstock with additives in fermentation or reaction process vessels. | Rebuild, repair, or replace biofuels processing equipment components.</t>
+  </si>
+  <si>
+    <t>51-9011.00</t>
+  </si>
+  <si>
+    <t>Chemical Equipment Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Chemical Operator | Chlorination Operator | Multiskill Operator | Outside Operator | Process Operator | Spray Dry Operator | Vessel Operator</t>
+  </si>
+  <si>
+    <t>IBM Notes | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational databases | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Active Listening | Critical Thinking | Speaking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Production and Processing | Chemistry | Mechanical | Computers and Electronics | English Language | Mathematics | Public Safety and Security | Law and Government | Administrative | Administration and Management | Engineering and Technology | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Control Precision | Near Vision | Written Comprehension | Perceptual Speed | Far Vision | Multilimb Coordination | Information Ordering | Manual Dexterity | Reaction Time | Written Expression | Deductive Reasoning | Speech Clarity | Speech Recognition | Rate Control | Arm-Hand Steadiness | Selective Attention | Flexibility of Closure | Inductive Reasoning | Auditory Attention | Visual Color Discrimination | Finger Dexterity | Visualization | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Hazardous Conditions | Health and Safety of Other Workers | E-Mail | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Pace Determined by Speed of Equipment | Contact With Others | Outdoors, Exposed to All Weather Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Consequence of Error | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Frequency of Decision Making | Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Chemical Engineers | Chemical Plant and System Operators | Chemical Technicians | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Semiconductor Processing Technicians | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Operate or tend equipment to control chemical changes or reactions in the processing of industrial or consumer products. Equipment used includes devulcanizers, steam-jacketed kettles, and reactor vessels.</t>
+  </si>
+  <si>
+    <t>Add treating or neutralizing agents to products, and pump products through filters or centrifuges to remove impurities or to precipitate products. | Adjust controls to regulate temperature, pressure, feed, or flow of liquids or gases and times of prescribed reactions, according to knowledge of equipment and processes. | Control or operate equipment in which chemical changes or reactions take place during the processing of industrial or consumer products. | Direct activities of workers assisting in control or verification of processes or in unloading of materials. | Drain equipment, and pump water or other solutions through to flush and clean tanks or equipment. | Draw samples of products at specified stages so that analyses can be performed. | Dump or scoop prescribed solid, granular, or powdered materials into equipment. | Estimate materials required for production and manufacturing of products. | Flush or clean equipment, using steam hoses or mechanical reamers. | Implement appropriate industrial emergency response procedures. | Inspect equipment or units to detect leaks or malfunctions, shutting equipment down, if necessary. | Inventory supplies received and consumed. | Make minor repairs, lubricate, and maintain equipment, using hand tools. | Measure, weigh, and mix chemical ingredients, according to specifications. | Monitor gauges, recording instruments, flowmeters, or products to ensure that specified conditions are maintained. | Notify maintenance engineers of equipment malfunctions. | Observe and compare colors and consistencies of products to instrument readings and to laboratory and standard test results. | Observe safety precautions to prevent fires or explosions. | Open valves or start pumps, agitators, reactors, blowers, or automatic feed of materials. | Patrol work areas to detect leaks or equipment malfunctions or to monitor operating conditions. | Read plant specifications to determine products, ingredients, or prescribed modifications of plant procedures. | Record operational data, such as temperatures, pressures, ingredients used, processing times, or test results. | Test product samples for specific gravity, chemical characteristics, pH levels, concentrations, or viscosities, or send them to laboratories for testing.</t>
+  </si>
+  <si>
+    <t>51-9012.00</t>
+  </si>
+  <si>
+    <t>Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Blender | Brewer | Cellar Worker | Digester Cook | Machine Tender | Paper Machine Tender | Plant Operator | Pulper Operator | Winemaker</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Perceptual Speed | Problem Sensitivity | Arm-Hand Steadiness | Information Ordering | Reaction Time | Static Strength | Multilimb Coordination | Control Precision | Selective Attention | Flexibility of Closure | Oral Comprehension | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Oral Expression | Speech Recognition | Hearing Sensitivity | Visual Color Discrimination | Far Vision | Gross Body Equilibrium | Extent Flexibility | Trunk Strength | Rate Control | Finger Dexterity | Manual Dexterity | Visualization</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Conflict Situations | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Hazardous Equipment | Degree of Automation</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Pump Operators, Except Wellhead Pumpers | Textile Bleaching and Dyeing Machine Operators and Tenders | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend continuous flow or vat-type equipment; filter presses; shaker screens; centrifuges; condenser tubes; precipitating, fermenting, or evaporating tanks; scrubbing towers; or batch stills. These machines extract, sort, or separate liquids, gases, or solids from other materials to recover a refined product. Includes dairy processing equipment operators.</t>
+  </si>
+  <si>
+    <t>Assemble fittings, valves, bowls, plates, disks, impeller shafts, or other parts to prepare equipment for operation. | Clean or sterilize tanks, screens, inflow pipes, production areas, or equipment, using hoses, brushes, scrapers, or chemical solutions. | Collect samples of materials or products for laboratory analysis. | Communicate processing instructions to other workers. | Connect pipes between vats and processing equipment. | Dump, pour, or load specified amounts of refined or unrefined materials into equipment or containers for further processing or storage. | Examine samples to verify qualities such as clarity, cleanliness, consistency, dryness, or texture. | Inspect machines or equipment for hazards, operating efficiency, malfunctions, wear, or leaks. | Install, maintain, or repair hoses, pumps, filters, or screens to maintain processing equipment, using hand tools. | Maintain logs of instrument readings, test results, or shift production for entry in computer databases. | Measure or weigh materials to be refined, mixed, transferred, stored, or otherwise processed. | Monitor material flow or instruments, such as temperature or pressure gauges, indicators, or meters, to ensure optimal processing conditions. | Operate machines to process materials in compliance with applicable safety, energy, or environmental regulations. | Remove clogs, defects, or impurities from machines, tanks, conveyors, screens, or other processing equipment. | Remove full containers from discharge outlets and replace them with empty containers. | Set up or adjust machine controls to regulate conditions such as material flow, temperature, or pressure. | Start agitators, shakers, conveyors, pumps, or centrifuge machines. | Test samples to determine viscosity, acidity, specific gravity, or degree of concentration, using test equipment such as viscometers, pH meters, or hydrometers. | Turn valves or move controls to admit, drain, separate, filter, clarify, mix, or transfer materials. | Turn valves to pump sterilizing solutions or rinse water through pipes or equipment or to spray vats with atomizers.</t>
+  </si>
+  <si>
+    <t>51-9021.00</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Beveler Operator | Cullet Trucker | Grinder | Grinder Operator | Machine Operator | Machine Tender | Miller | Polisher | Preparation Operator (Prep Operator) | Pulverizer</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Administration and Management | Production and Processing | English Language | Education and Training | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Control Precision | Reaction Time | Rate Control | Multilimb Coordination | Arm-Hand Steadiness | Near Vision | Problem Sensitivity | Auditory Attention | Trunk Strength | Static Strength | Finger Dexterity | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Hearing Sensitivity | Visual Color Discrimination | Extent Flexibility | Response Orientation | Selective Attention | Visualization | Category Flexibility | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Health and Safety of Other Workers | Pace Determined by Speed of Equipment | Determine Tasks, Priorities and Goals | Consequence of Error | Spend Time Standing | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Impact of Decisions on Co-workers or Company Results | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Mixing and Blending Machine Setters, Operators, and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines to crush, grind, or polish materials, such as coal, glass, grain, stone, food, or rubber.</t>
+  </si>
+  <si>
+    <t>Add or mix chemicals and ingredients for processing, using hand tools or other devices. | Clean work areas. | Clean, adjust, and maintain equipment, using hand tools. | Collect samples of materials or products for laboratory testing. | Dislodge and clear jammed materials or other items from machinery and equipment, using hand tools. | Examine materials, ingredients, or products, visually or with hands, to ensure conformance to established standards. | Inspect chains, belts, or scrolls for signs of wear. | Load materials into machinery and equipment, using hand tools. | Mark bins as to types of mixtures stored. | Move controls to start, stop, or adjust machinery and equipment that crushes, grinds, polishes, or blends materials. | Notify supervisors of needed repairs. | Observe operation of equipment to ensure continuity of flow, safety, and efficient operation, and to detect malfunctions. | Read work orders to determine production specifications and information. | Record data from operations, testing, and production on specified forms. | Reject defective products and readjust equipment to eliminate problems. | Set mill gauges to specified fineness of grind. | Tend accessory equipment, such as pumps and conveyors, to move materials or ingredients through production processes. | Test samples of materials or products to ensure compliance with specifications, using test equipment. | Transfer materials, supplies, and products between work areas, using moving equipment and hand tools. | Turn valves to regulate the moisture contents of materials. | Weigh or measure materials, ingredients, or products at specified intervals to ensure conformance to requirements.</t>
+  </si>
+  <si>
+    <t>51-9022.00</t>
+  </si>
+  <si>
+    <t>Grinding and Polishing Workers, Hand</t>
+  </si>
+  <si>
+    <t>Buffer | Casting Finisher | Chipper | Finisher | Grinder | Jewelry Polisher | Knife Grinder | Metal Finisher | Polisher | Stand Grinder</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Finger Dexterity | Control Precision | Near Vision | Manual Dexterity | Multilimb Coordination | Speech Clarity | Speech Recognition | Selective Attention | Information Ordering | Problem Sensitivity | Oral Comprehension | Flexibility of Closure | Category Flexibility | Oral Expression | Visualization | Perceptual Speed | Visual Color Discrimination | Trunk Strength | Rate Control</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Time Pressure | Contact With Others | Spend Time Standing | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Shoe Machine Operators and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Grind, sand, or polish, using hand tools or hand-held power tools, a variety of metal, wood, stone, clay, plastic, or glass objects. Includes chippers, buffers, and finishers.</t>
+  </si>
+  <si>
+    <t>Apply solutions and chemicals to equipment, objects, or parts, using hand tools. | Clean brass particles from files by drawing file cards through file grooves. | File grooved, contoured, and irregular surfaces of metal objects, such as metalworking dies and machine parts, to conform to templates, other parts, layouts, or blueprint specifications. | Grind, sand, clean, or polish objects or parts to correct defects or to prepare surfaces for further finishing, using hand tools and power tools. | Load and adjust workpieces onto equipment or work tables, using hand tools. | Mark defects, such as knotholes, cracks, and splits, for repair. | Measure and mark equipment, objects, or parts to ensure grinding and polishing standards are met. | Move controls to adjust, start, or stop equipment during grinding and polishing processes. | Record product and processing data on specified forms. | Remove completed workpieces from equipment or work tables, using hand tools, and place workpieces in containers. | Repair and maintain equipment, objects, or parts, using hand tools. | Select files or other abrasives, according to materials, sizes and shapes of workpieces, amount of stock to be removed, finishes specified, and steps in finishing processes. | Sharpen abrasive grinding tools, using machines and hand tools. | Study blueprints or layouts to determine how to lay out workpieces or saw out templates. | Transfer equipment, objects, or parts to specified work areas, using moving devices. | Trim, scrape, or deburr objects or parts, using chisels, scrapers, and other hand tools and equipment. | Verify quality of finished workpieces by inspecting them, comparing them to templates, measuring their dimensions, or testing them in working machinery.</t>
+  </si>
+  <si>
+    <t>51-9023.00</t>
+  </si>
+  <si>
+    <t>Mixing and Blending Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Batchmaker | Blender | Blending Technician (Blending Tech) | Ink Blender | Issuing Operator | Machine Operator | Mixer | Mixer Operator | Operator | Stock Preparation Operator (Stock Prep Operator)</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Operational databases | SAP software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Manual Dexterity | Far Vision | Reaction Time | Multilimb Coordination | Control Precision | Selective Attention | Perceptual Speed | Category Flexibility | Information Ordering | Problem Sensitivity | Written Comprehension | Oral Comprehension | Rate Control | Response Orientation | Finger Dexterity | Inductive Reasoning | Deductive Reasoning | Oral Expression | Trunk Strength | Static Strength | Speech Clarity | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Exposed to Hazardous Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Repeating Same Tasks | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Pace Determined by Speed of Equipment | Impact of Decisions on Co-workers or Company Results | Contact With Others | Spend Time Making Repetitive Motions | Exposed to Hazardous Equipment | Consequence of Error | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Chemical Equipment Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Batchmakers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines to mix or blend materials, such as chemicals, tobacco, liquids, color pigments, or explosive ingredients.</t>
+  </si>
+  <si>
+    <t>Add or mix chemicals or ingredients for processing, using hand tools or other devices. | Clean and maintain equipment, using hand tools. | Clean work areas. | Collect samples of materials or products for laboratory testing. | Compound or process ingredients or dyes, according to formulas. | Dislodge and clear jammed materials or other items from machinery or equipment, using hand tools. | Dump or pour specified amounts of materials into machinery or equipment. | Examine materials, ingredients, or products visually or with hands to ensure conformance to established standards. | Mix or blend ingredients by starting machines and mixing for specified times. | Observe production or monitor equipment to ensure safe and efficient operation. | Open valves to drain slurry from mixers into storage tanks. | Operate or tend machines to mix or blend any of a wide variety of materials, such as spices, dough batter, tobacco, fruit juices, chemicals, livestock feed, food products, color pigments, or explosive ingredients. | Read work orders to determine production specifications or information. | Record operational or production data on specified forms. | Stop mixing or blending machines when specified product qualities are obtained and open valves and start pumps to transfer mixtures. | Tend accessory equipment, such as pumps or conveyors, to move materials or ingredients through production processes. | Test samples of materials or products to ensure compliance with specifications, using test equipment. | Transfer materials, supplies, or products between work areas, using moving equipment or hand tools. | Unload mixtures into containers or onto conveyors for further processing. | Weigh or measure materials, ingredients, or products to ensure conformance to requirements.</t>
+  </si>
+  <si>
+    <t>51-9031.00</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand</t>
+  </si>
+  <si>
+    <t>Cloth Cutter | Denim Cutter | Fabric Cutter | Finisher | Glass Cutter | Hand Cutter | Leather Cutter | Offline Cutter | Sample Cutter | Trimmer</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking | Mathematics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Arm-Hand Steadiness | Information Ordering | Speech Recognition | Static Strength | Control Precision | Category Flexibility | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Standing | Spend Time Making Repetitive Motions | Time Pressure</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Packers and Packagers, Hand | Painting, Coating, and Decorating Workers | Paper Goods Machine Setters, Operators, and Tenders | Sawing Machine Setters, Operators, and Tenders, Wood | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Use hand tools or hand-held power tools to cut and trim a variety of manufactured items, such as carpet, fabric, stone, glass, or rubber.</t>
+  </si>
+  <si>
+    <t>Adjust guides and stops to control depths and widths of cuts. | Clean, treat, buff, or polish finished items, using grinders, brushes, chisels, and cleaning solutions and polishing materials. | Count or weigh and bundle items. | Cut, shape, and trim materials, such as textiles, food, glass, stone, and metal, using knives, scissors, and other hand tools, portable power tools, or bench-mounted tools. | Fold or shape materials before or after cutting them. | Lower table-mounted cutters such as knife blades, cutting wheels, or saws to cut items to specified sizes. | Mark cutting lines around patterns or templates, or follow layout points, using squares, rules, and straightedges, and chalk, pencils, or scribes. | Mark identification numbers, trademarks, grades, marketing data, sizes, or model numbers on products. | Mark or discard items with defects such as spots, stains, scars, snags, chips, scratches, or unacceptable shapes or finishes. | Position templates or measure materials to locate specified points of cuts or to obtain maximum yields, using rules, scales, or patterns. | Read work orders to determine dimensions, cutting locations, and quantities to cut. | Replace or sharpen dulled cutting tools such as saws. | Route items to provide cutouts for parts, using portable routers, grinders, and hand tools. | Separate materials or products according to size, weight, type, condition, color, or shade. | Stack cut items and load them on racks or conveyors or onto trucks. | Transport items to work or storage areas, using carts. | Trim excess material or cut threads off finished products, such as cutting loose ends of plastic off a manufactured toy for a smoother finish. | Unroll, lay out, attach, or mount materials or items on cutting tables or machines.</t>
+  </si>
+  <si>
+    <t>51-9032.00</t>
+  </si>
+  <si>
+    <t>Cutting and Slicing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Cutter | Cutter Operator | Cutting Pressman | Die Cutter Operator | Flat Cutter | Machine Operator | Paper Cutter | Sheeter | Skiver Operator | Slitter</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Outlook | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | Mechanical</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Control Precision | Near Vision | Arm-Hand Steadiness | Problem Sensitivity | Manual Dexterity | Visualization | Oral Comprehension | Reaction Time | Multilimb Coordination | Rate Control | Deductive Reasoning | Information Ordering | Selective Attention | Depth Perception | Extent Flexibility | Trunk Strength | Static Strength | Perceptual Speed | Category Flexibility | Written Comprehension | Response Orientation | Inductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Pace Determined by Speed of Equipment | Time Pressure | Importance of Repeating Same Tasks | Spend Time Walking or Running | Exposed to Contaminants | Contact With Others | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Shoe Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines that cut or slice materials, such as glass, stone, cork, rubber, tobacco, food, paper, or insulating material.</t>
+  </si>
+  <si>
+    <t>Adjust machine controls to alter position, alignment, speed, or pressure. | Change or replace saw blades, cables, cutter heads, and grinding wheels, using hand tools. | Clean and lubricate cutting machines, conveyors, blades, saws, or knives, using steam hoses, scrapers, brushes, or oil cans. | Cut stock manually to prepare for machine cutting, using tools such as knives, cleavers, handsaws, or hammers and chisels. | Direct workers on cutting teams. | Examine, measure, and weigh materials or products to verify conformance to specifications, using measuring devices, such as rulers, micrometers, or scales. | Feed stock into cutting machines, onto conveyors, or under cutting blades, by threading, guiding, pushing, or turning handwheels. | Maintain production records, such as quantities, types, and dimensions of materials produced. | Mark cutting lines or identifying information on stock, using marking pencils, rulers, or scribes. | Monitor operation of cutting or slicing machines to detect malfunctions or to determine whether supplies need replenishment. | Move stock or scrap to and from machines manually, or by using carts, handtrucks, or lift trucks. | Position stock along cutting lines, or against stops on beds of scoring or cutting machines. | Position width gauge blocks between blades, and level blades and insert wedges into frames to secure blades to frames. | Press buttons, pull levers, or depress pedals to start and operate cutting and slicing machines. | Remove completed materials or products from cutting or slicing machines, and stack or store them for additional processing. | Remove defective or substandard materials from machines, and readjust machine components so that products meet standards. | Review work orders, blueprints, specifications, or job samples to determine components, settings, and adjustments for cutting and slicing machines. | Select and install machine components, such as cutting blades, rollers, and templates, according to specifications, using hand tools. | Set up, operate, or tend machines that cut or slice materials, such as glass, stone, cork, rubber, tobacco, food, paper, or insulating material. | Sharpen cutting blades, knives, or saws, using files, bench grinders, or honing stones. | Stack and sort cut material for packaging, further processing, or shipping, according to types and sizes of material. | Start machines to verify setups, and make any necessary adjustments. | Tighten pulleys or add abrasives to maintain cutting speeds. | Turn cranks or press buttons to activate winches that move cars under sawing cables or saw frames. | Type instructions on computer keyboards, push buttons to activate computer programs, or manually set cutting guides, clamps, and knives.</t>
+  </si>
+  <si>
+    <t>51-9041.00</t>
+  </si>
+  <si>
+    <t>Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Extruder Operator | Extrusion Operator | Glass Forming Crew Member | Machine Operator | Press Operator | Tuber Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Operational databases | Production scheduling software | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Perceptual Speed | Rate Control | Reaction Time | Arm-Hand Steadiness | Near Vision | Manual Dexterity | Problem Sensitivity | Information Ordering | Finger Dexterity | Control Precision | Far Vision | Auditory Attention | Stamina | Trunk Strength | Static Strength | Multilimb Coordination | Selective Attention | Visualization | Category Flexibility | Deductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Inductive Reasoning | Speech Clarity | Speech Recognition | Hearing Sensitivity | Depth Perception | Response Orientation</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Exposed to Contaminants | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Exposed to Very Hot or Cold Temperatures | Time Pressure | Frequency of Decision Making | Importance of Repeating Same Tasks | Physical Proximity | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Spend Time Walking or Running | Freedom to Make Decisions | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines, such as glass-forming machines, plodder machines, and tuber machines, to shape and form products such as glassware, food, rubber, soap, brick, tile, clay, wax, tobacco, or cosmetics.</t>
+  </si>
+  <si>
+    <t>Activate machines to shape or form products, such as candy bars, light bulbs, balloons, or insulation panels. | Adjust machine components to regulate speeds, pressures, and temperatures, and amounts, dimensions, and flow of materials or ingredients. | Clean dies, arbors, compression chambers, and molds, using swabs, sponges, or air hoses. | Clear jams, and remove defective or substandard materials or products. | Complete work tickets, and place them with products. | Couple air and gas lines to machines to maintain plasticity of material and to regulate solidification of final products. | Disassemble equipment to repair it or to replace parts, such as nozzles, punches, and filters. | Examine, measure, and weigh materials or products to verify conformance to standards, using measuring devices such as templates, micrometers, or scales. | Feed products into machines by hand or conveyor. | Install, align, and adjust neck rings, press plungers, and feeder tubes. | Measure arbors and dies to verify sizes specified on work tickets. | Measure, mix, cut, shape, soften, and join materials and ingredients, such as powder, cornmeal, or rubber to prepare them for machine processing. | Monitor machine operations and observe lights and gauges to detect malfunctions. | Move materials, supplies, components, and finished products between storage and work areas, using work aids such as racks, hoists, and handtrucks. | Notify supervisors when extruded filaments fail to meet standards. | Pour, scoop, or dump specified ingredients, metal assemblies, or mixtures into sections of machine prior to starting machines. | Press control buttons to activate machinery and equipment. | Record and maintain production data, such as meter readings, and quantities, types, and dimensions of materials produced. | Remove materials or products from molds or from extruding, forming, pressing, or compacting machines, and stack or store them for additional processing. | Remove molds, mold components, and feeder tubes from machinery after production is complete. | Review work orders, specifications, or instructions to determine materials, ingredients, procedures, components, settings, and adjustments for extruding, forming, pressing, or compacting machines. | Select and install machine components, such as dies, molds, and cutters, according to specifications, using hand tools and measuring devices. | Send product samples to laboratories for analysis. | Swab molds with solutions to prevent products from sticking. | Synchronize speeds of sections of machines when producing products involving several steps or processes. | Turn controls to adjust machine functions, such as regulating air pressure, creating vacuums, and adjusting coolant flow.</t>
+  </si>
+  <si>
+    <t>51-9051.00</t>
+  </si>
+  <si>
+    <t>Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Annealing Operator | Dry Kiln Operator | Dryer Feeder | Evaporator Operator | Furnace Operator | Kiln Fireman | Kiln Operator | Lime Kiln and Recausticizing Operator | Oven Operator</t>
+  </si>
+  <si>
+    <t>Inventory tracking software | Machine operation software | Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Control Precision | Written Comprehension | Oral Comprehension | Speech Recognition | Arm-Hand Steadiness | Near Vision | Speech Clarity | Reaction Time | Selective Attention | Information Ordering | Oral Expression | Inductive Reasoning | Deductive Reasoning | Manual Dexterity | Perceptual Speed | Trunk Strength | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings | Consequence of Error | Work Outcomes and Results of Other Workers | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Contact With Others | Exposed to Hazardous Equipment | Pace Determined by Speed of Equipment | Freedom to Make Decisions | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend heating equipment other than basic metal, plastic, or food processing equipment. Includes activities such as annealing glass, drying lumber, curing rubber, removing moisture from materials, or boiling soap.</t>
+  </si>
+  <si>
+    <t>Calculate amounts of materials to be loaded into furnaces, adjusting amounts as necessary for specific conditions. | Clean, lubricate, and adjust equipment, using scrapers, solvents, air hoses, oil, and hand tools. | Confer with supervisors or other equipment operators to report equipment malfunctions or to resolve production problems. | Direct crane operators and crew members to load vessels with materials to be processed. | Examine or test samples of processed substances, or collect samples for laboratory testing, to ensure conformance to specifications. | Feed fuel, such as coal and coke, into fireboxes or onto conveyors, and remove ashes from furnaces, using shovels and buckets. | Load equipment receptacles or conveyors with material to be processed, by hand or using hoists. | Melt or refine metal before casting, calculating required temperatures, and observe metal color, adjusting controls as necessary to maintain required temperatures. | Monitor equipment operation, gauges, and panel lights to detect deviations from standards. | Press and adjust controls to activate, set, and regulate equipment according to specifications. | Read and interpret work orders and instructions to determine work assignments, process specifications, and production schedules. | Record gauge readings, test results, and shift production in log books. | Remove products from equipment, manually or using hoists, and prepare them for storage, shipment, or additional processing. | Replace worn or defective equipment parts, using hand tools. | Stop equipment and clear blockages or jams, using fingers, wire, or hand tools. | Transport materials and products to and from work areas, manually or using carts, handtrucks, or hoists. | Weigh or measure specified amounts of ingredients or materials for processing, using devices such as scales and calipers.</t>
+  </si>
+  <si>
+    <t>51-9061.00</t>
+  </si>
+  <si>
+    <t>Inspectors, Testers, Sorters, Samplers, and Weighers</t>
+  </si>
+  <si>
+    <t>Inspector | QA Auditor (Quality Assurance Auditor) | QA Inspector (Quality Assurance Inspector) | QA Technician (Quality Assurance Technician) | QC Technician (Quality Control Technician) | Quality Auditor | Quality Control Inspector (QC Inspector) | Quality Inspector | Quality Technician | Test Technician</t>
+  </si>
+  <si>
+    <t>Apache Hive | Apache Pig | Atlassian JIRA | Autodesk AutoCAD | Computer assisted design software | Computer-aided inspection software | Coordinate measuring machine software | Cybermetrics GAGETrak | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Data analysis software | Data entry software | Database software | Design of experiments DOE software | Extensible markup language XML | FileMaker Pro | IBM Lotus Notes | IBM Notes | Inspection marking systems | Label inspection systems | Mastercam Design | Mastercam computer-aided design and manufacturing software | Medical condition coding software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Minitab | R | SAP software | Selenium | Skype | Statistical process control SPC data collection devices | Structured query language SQL | The MathWorks MATLAB | Tolerance analysis software | Verisurf Metrology | Wilcox Associates PC-DMIS Inspection Planner</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Writing | Speaking | Reading Comprehension | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language | Customer and Personal Service | Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Near Vision | Oral Comprehension | Perceptual Speed | Problem Sensitivity | Flexibility of Closure | Category Flexibility | Information Ordering | Written Comprehension | Speech Clarity | Speech Recognition | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Visualization | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Not Environmentally Controlled | Exposed to Contaminants | E-Mail | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Spend Time Standing | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Time Pressure | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Machinists | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Timing Device Assemblers and Adjusters | Weighers, Measurers, Checkers, and Samplers, Recordkeeping | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Inspect, test, sort, sample, or weigh nonagricultural raw materials or processed, machined, fabricated, or assembled parts or products for defects, wear, and deviations from specifications. May use precision measuring instruments and complex test equipment.</t>
+  </si>
+  <si>
+    <t>Adjust, clean, or repair products or processing equipment to correct defects found during inspections. | Administer tests to assess whether engineers or operators are qualified to use equipment. | Analyze test data, making computations as necessary, to determine test results. | Check arriving materials to ensure that they match purchase orders, submitting discrepancy reports as necessary. | Clean, maintain, calibrate, or repair measuring instruments or test equipment, such as dial indicators, fixed gauges, or height gauges. | Collect or select samples for testing or for use as models. | Compare colors, shapes, textures, or grades of products or materials with color charts, templates, or samples to verify conformance to standards. | Compute defect percentages or averages, using formulas and calculators. | Compute usable amounts of items in shipments. | Disassemble defective parts or components, such as inaccurate or worn gauges or measuring instruments. | Discard or reject products, materials, or equipment not meeting specifications. | Fabricate, install, position, or connect components, parts, finished products, or instruments for testing or operational purposes. | Grade, classify, or sort products according to sizes, weights, colors, or other specifications. | Inspect or test raw materials, parts, or products to determine compliance with environmental standards. | Inspect, test, or measure materials, products, installations, or work for conformance to specifications. | Interpret legal requirements, provide safety information, or recommend compliance procedures to contractors, craft workers, engineers, or property owners. | Make minor adjustments to equipment, such as turning setscrews to calibrate instruments to required tolerances. | Mark items with details, such as grade or acceptance-rejection status. | Measure dimensions of products to verify conformance to specifications, using measuring instruments, such as rulers, calipers, gauges, or micrometers. | Monitor machines that automatically measure, sort, or inspect products. | Monitor production operations or equipment to ensure conformance to specifications, making necessary process or assembly adjustments. | Notify supervisors or other personnel of production problems. | Position products, components, or parts for testing. | Read blueprints, data, manuals, or other materials to determine specifications, inspection and testing procedures, adjustment methods, certification processes, formulas, or measuring instruments required. | Read dials or meters to verify that equipment is functioning at specified levels. | Recommend necessary corrective actions, based on inspection results. | Record inspection or test data, such as weights, temperatures, grades, or moisture content, and quantities inspected or graded. | Remove defects, such as chips, burrs, or lap corroded or pitted surfaces. | Stack or arrange tested products for further processing, shipping, or packaging. | Weigh materials, products, containers, or samples to verify packaging weights or ingredient quantities. | Write test or inspection reports describing results, recommendations, or needed repairs.</t>
+  </si>
+  <si>
+    <t>51-9071.00</t>
+  </si>
+  <si>
+    <t>Jewelers and Precious Stone and Metal Workers</t>
+  </si>
+  <si>
+    <t>Appraiser | Artisan Jeweler | Bench Jeweler | Caster | Gemologist | Goldsmith | Jeweler | Polisher | Silversmith | Stone Setter</t>
+  </si>
+  <si>
+    <t>Adobe Illustrator | Adobe Photoshop | Computer assisted jewelry design CAD software | Customer information databases | Intuit QuickBooks | Inventory tracking software | Jewelry store point of sale POS software | Metal designing software | Microsoft Excel | Microsoft Outlook | Microsoft Word | Retail management software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Design | Production and Processing | Sales and Marketing | Administration and Management | Mechanical | Engineering and Technology | Mathematics | Administrative | Fine Arts | Economics and Accounting | Education and Training</t>
+  </si>
+  <si>
+    <t>Near Vision | Finger Dexterity | Arm-Hand Steadiness | Oral Comprehension | Visualization | Category Flexibility | Originality | Oral Expression | Speech Recognition | Visual Color Discrimination | Information Ordering | Deductive Reasoning | Problem Sensitivity | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Time Pressure | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Contact With Others | Telephone Conversations | Work With or Contribute to a Work Group or Team | Spend Time Sitting | E-Mail | Exposed to Contaminants | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Cabinetmakers and Bench Carpenters | Craft Artists | Cutters and Trimmers, Hand | Etchers and Engravers | Furniture Finishers | Gem and Diamond Workers | Glass Blowers, Molders, Benders, and Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Layout Workers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Patternmakers, Wood | Sewers, Hand | Shoe and Leather Workers and Repairers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Design, fabricate, adjust, repair, or appraise jewelry, gold, silver, other precious metals, or gems.</t>
+  </si>
+  <si>
+    <t>Anneal precious metal objects such as coffeepots, tea sets, and trays in gas ovens for prescribed times to soften metal for reworking. | Buy and sell jewelry, or serve as agents between buyers and sellers. | Clean and polish metal items and jewelry pieces, using jewelers' tools, polishing wheels, and chemical baths. | Compute costs of labor and materials to determine production costs of products and articles. | Construct preliminary models of wax, metal, clay, or plaster, and form sample castings in molds. | Create jewelry from materials such as gold, silver, platinum, and precious or semiprecious stones. | Create new jewelry designs and modify existing designs, using computers as necessary. | Cut and file pieces of jewelry such as rings, brooches, bracelets, and lockets. | Cut designs in molds or other materials to be used as models in the fabrication of metal and jewelry products. | Design and fabricate molds, models, and machine accessories, and modify hand tools used to cast metal and jewelry pieces. | Determine appraised values of diamonds and other gemstones based on price guides, market fluctuations, and stone grades and rarity. | Examine assembled or finished products to ensure conformance to specifications, using magnifying glasses or precision measuring instruments. | Grade stones based on their color, perfection, and quality of cut. | Lay out designs on metal stock, and cut along markings to fabricate pieces used to cast metal molds. | Make repairs, such as enlarging or reducing ring sizes, soldering pieces of jewelry together, and replacing broken clasps and mountings. | Mark, engrave, or emboss designs on metal pieces such as castings, wire, or jewelry, following specifications. | Pierce and cut open designs in ornamentation, using hand drills and scroll saws. | Plate articles such as jewelry pieces and watch dials, using silver, gold, nickel, or other metals. | Position stones and metal pieces, and set, mount, and secure items in place, using setting and hand tools. | Pour molten metal alloys or other materials into molds to cast models of jewelry. | Record the weights and processing times of finished pieces. | Research and analyze reference materials, and consult with interested parties to develop new products or modify existing designs. | Rotate molds to distribute alloys and to prevent formation of air pockets. | Rout out locations where parts are to be joined to items, using routing machines. | Select and acquire metals and gems for designs. | Shape and straighten damaged or twisted articles by hand or using pliers. | Smooth soldered joints and rough spots, using hand files and emery paper, and polish smoothed areas with polishing wheels or buffing wire. | Soften metal to be used in designs by heating it with a gas torch and shape it, using hammers and dies. | Weigh, mix, and melt metal alloys or materials needed for jewelry models. | Write or modify design specifications such as the metal contents and weights of items.</t>
+  </si>
+  <si>
+    <t>51-9071.06</t>
+  </si>
+  <si>
+    <t>Gem and Diamond Workers</t>
+  </si>
+  <si>
+    <t>Diamond Cutter | Diamond Grader | Diamond Picker | Diamond Polisher | Diamond Sawer | Diamond Setter | Facetor | Gemologist | Lapidarist</t>
+  </si>
+  <si>
+    <t>Business accounting software | Gem identification databases | GemCad | Inventory tracking software | Jewelry design software | Spectrophotometer analysis software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Production and Processing | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Finger Dexterity | Arm-Hand Steadiness | Visual Color Discrimination | Problem Sensitivity | Control Precision | Manual Dexterity | Flexibility of Closure | Category Flexibility | Deductive Reasoning | Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Selective Attention | Visualization | Information Ordering</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Sitting | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Written Letters and Memos | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Contaminants | Spend Time Making Repetitive Motions | Time Pressure</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Etchers and Engravers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Jewelers and Precious Stone and Metal Workers | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Ophthalmic Laboratory Technicians | Painting, Coating, and Decorating Workers | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Rock Splitters, Quarry | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Stone Cutters and Carvers, Manufacturing | Timing Device Assemblers and Adjusters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Watch and Clock Repairers</t>
+  </si>
+  <si>
+    <t>Fabricate, finish, or evaluate the quality of gems and diamonds used in jewelry or industrial tools.</t>
+  </si>
+  <si>
+    <t>Advise customers and others on the best use of gems to create attractive jewelry items. | Assign polish, symmetry, and clarity grades to stones, according to established grading systems. | Dismantle lapping, boring, cutting, polishing, and shaping equipment and machinery to clean and lubricate it. | Estimate wholesale and retail value of gems, following pricing guides, market fluctuations, and other relevant economic factors. | Examine diamonds or gems to ascertain the shape, cut, and width of cut stones, or to select the cuts that will result in the biggest, best quality stones. | Examine gem surfaces and internal structures, using polariscopes, refractometers, microscopes, and other optical instruments, to differentiate between stones, to identify rare specimens, or to detect flaws, defects, or peculiarities affecting gem values. | Examine gems during processing to ensure accuracy of angles and positions of cuts or bores, using magnifying glasses, loupes, or shadowgraphs. | Hold stones, gems, dies, or styluses against rotating plates, wheels, saws, or slitters to cut, shape, slit, grind, or polish them. | Identify and document stones' clarity characteristics, using plot diagrams. | Immerse stones in prescribed chemical solutions to determine specific gravities and key properties of gemstones or substitutes. | Measure sizes of stones' bore holes and cuts to ensure adherence to specifications, using precision measuring instruments. | Secure gems or diamonds in holders, chucks, dops, lapidary sticks, or blocks for cutting, polishing, grinding, drilling, or shaping. | Select shaping wheels for tasks, and mix and apply abrasives, bort, or polishing compounds. | Sort rough diamonds into categories based on shape, size, color, and quality.</t>
+  </si>
+  <si>
+    <t>51-9081.00</t>
+  </si>
+  <si>
+    <t>Dental Laboratory Technicians</t>
+  </si>
+  <si>
+    <t>Ceramist | Crown and Bridge Dental Laboratory Technician (Crown and Bridge Dental Lab Tech) | Dental Ceramist | Dental Laboratory Technician (Dental Lab Tech) | Dental Technician (Dental Tech) | Denture Technician (Denture Tech) | Metal Finisher | Orthodontic Laboratory Technician (Ortho Lab Tech) | Porcelain Technician (Porcelain Tech) | Waxer</t>
+  </si>
+  <si>
+    <t>Bookkeeping software | Computer aided design and drafting CADD software | Computer imaging software | Database management software | Dental product design software | Dental product manufacturing software | Easy Solutions Easy Lab | Email software | Graphics software | Intuit QuickBooks | Inventrix Labtrac | Jenmar International DL-Plus | LabMagic | Laboratory Systems Group Lab Manager | Mainstreet Systems &amp; Software DentaLab/PC II | Mainstreet Systems &amp; Software DentaRX | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Scheduling software | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Learning | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Administration and Management | Design | English Language | Medicine and Dentistry | Production and Processing | Education and Training | Customer and Personal Service | Mechanical | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Near Vision | Arm-Hand Steadiness | Control Precision | Visualization | Information Ordering | Deductive Reasoning | Problem Sensitivity | Selective Attention | Manual Dexterity | Written Comprehension | Speech Clarity | Speech Recognition | Category Flexibility | Oral Comprehension | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Oral Expression | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Time Pressure | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Spend Time Sitting | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Exposed to Disease or Infections | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Dental Assistants | Dental Hygienists | Dentists, General | Endoscopy Technicians | Etchers and Engravers | Furniture Finishers | Grinding and Polishing Workers, Hand | Medical Appliance Technicians | Medical Equipment Repairers | Molders, Shapers, and Casters, Except Metal and Plastic | Ophthalmic Laboratory Technicians | Orthodontists | Orthotists and Prosthetists | Painting, Coating, and Decorating Workers | Prosthodontists | Structural Metal Fabricators and Fitters | Surgical Technologists | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Construct and repair full or partial dentures or dental appliances.</t>
+  </si>
+  <si>
+    <t>Apply porcelain paste or wax over prosthesis frameworks or setups, using brushes and spatulas. | Build and shape wax teeth, using small hand instruments and information from observations or dentists' specifications. | Create a model of patient's mouth by pouring plaster into a dental impression and allowing plaster to set. | Fabricate, alter, or repair dental devices, such as dentures, crowns, bridges, inlays, or appliances for straightening teeth. | Fill chipped or low spots in surfaces of devices, using acrylic resins. | Load newly constructed teeth into porcelain furnaces to bake the porcelain onto the metal framework. | Melt metals or mix plaster, porcelain, or acrylic pastes and pour materials into molds or over frameworks to form dental prostheses or apparatuses. | Mold wax over denture setups to form the full contours of artificial gums. | Place tooth models on an apparatus that mimics bite and movement of patient's jaw to evaluate functionality of model. | Prepare metal surfaces for bonding with porcelain to create artificial teeth, using small hand tools. | Prepare wax bite blocks and impression trays for use. | Read prescriptions or specifications and examine models or impressions to determine the design of dental products to be constructed. | Rebuild or replace linings, wire sections, or missing teeth to repair dentures. | Remove excess metal or porcelain and polish surfaces of prostheses or frameworks, using polishing machines. | Shape and solder wire and metal frames or bands for dental products, using soldering irons and hand tools. | Test appliances for conformance to specifications and accuracy of occlusion, using articulators and micrometers. | Train or supervise other dental technicians or dental laboratory bench workers.</t>
+  </si>
+  <si>
+    <t>51-9082.00</t>
+  </si>
+  <si>
+    <t>Medical Appliance Technicians</t>
+  </si>
+  <si>
+    <t>Certified Pedorthotist | Hearing Aid Repair Technician | Lab Technician | Orthopedic Technician | Orthotic Technician | Orthotic and Prosthetic Technician (O and P Technician) | Prosthetic Technician | Prosthetics Technician | Registered Prosthetic Orthotic Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Footmaxx Metascan software | Gait analysis software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Ohio Willow Wood OMEGA Tracer System | Orthotic fabrication software | Seattle Systems Shapemaker | SoftSource CADview | Vorum Research Corporation CANFIT-PLUS</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Reading Comprehension | Speaking | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Production and Processing | Customer and Personal Service | English Language | Mechanical | Design | Education and Training | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Near Vision | Oral Expression | Deductive Reasoning | Visualization | Arm-Hand Steadiness | Information Ordering | Finger Dexterity | Speech Clarity | Speech Recognition | Manual Dexterity | Inductive Reasoning | Multilimb Coordination | Control Precision | Written Comprehension | Originality | Written Expression | Visual Color Discrimination | Trunk Strength | Selective Attention | Category Flexibility | Hearing Sensitivity | Depth Perception</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Time Pressure | Frequency of Decision Making | Spend Time Standing | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Telephone Conversations | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Deal With External Customers or the Public in General | Health and Safety of Other Workers | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Dental Laboratory Technicians | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Endoscopy Technicians | Mechanical Engineering Technologists and Technicians | Medical Equipment Preparers | Medical Equipment Repairers | Molders, Shapers, and Casters, Except Metal and Plastic | Ophthalmic Laboratory Technicians | Orthopedic Surgeons, Except Pediatric | Orthotists and Prosthetists | Pediatric Surgeons | Sewers, Hand | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Structural Metal Fabricators and Fitters | Surgical Technologists | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Construct, maintain, or repair medical supportive devices such as braces, orthotics and prosthetic devices, joints, arch supports, and other surgical and medical appliances.</t>
+  </si>
+  <si>
+    <t>Bend, form, and shape fabric or material to conform to prescribed contours of structural components. | Construct or receive casts or impressions of patients' torsos or limbs for use as cutting and fabrication patterns. | Cover or pad metal or plastic structures or devices, using coverings such as rubber, leather, felt, plastic, or fiberglass. | Drill and tap holes for rivets, and glue, weld, bolt, or rivet parts together to form prosthetic or orthotic devices. | Fit appliances onto patients, and make any necessary adjustments. | Instruct patients in use of prosthetic or orthotic devices. | Lay out and mark dimensions of parts, using templates and precision measuring instruments. | Make orthotic or prosthetic devices, using materials such as thermoplastic and thermosetting materials, metal alloys and leather, and hand or power tools. | Mix pigments to match patients' skin coloring, according to formulas, and apply mixtures to orthotic or prosthetic devices. | Polish artificial limbs, braces, or supports, using grinding and buffing wheels. | Read prescriptions or specifications to determine the type of product or device to be fabricated and the materials and tools required. | Repair, modify, or maintain medical supportive devices, such as artificial limbs, braces, or surgical supports, according to specifications. | Service or repair machinery used in the fabrication of appliances. | Take patients' body or limb measurements for use in device construction. | Test medical supportive devices for proper alignment, movement, or biomechanical stability, using meters and alignment fixtures.</t>
+  </si>
+  <si>
+    <t>51-9083.00</t>
+  </si>
+  <si>
+    <t>Ophthalmic Laboratory Technicians</t>
+  </si>
+  <si>
+    <t>Edger Technician | Finishing Lab Technician | Lab Technician (Laboratory Technician) | Lens Grinder and Polisher | Line Operator | Optical Lab Technician (Optical Laboratory Technician) | Optical Technician | Polisher | Surfacing Technician</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Eyeglass design software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Finger Dexterity | Control Precision | Manual Dexterity | Deductive Reasoning | Problem Sensitivity | Selective Attention | Visualization | Information Ordering | Speech Recognition | Visual Color Discrimination | Wrist-Finger Speed | Reaction Time | Rate Control | Perceptual Speed | Flexibility of Closure | Category Flexibility | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Pace Determined by Speed of Equipment | Spend Time Standing | Exposed to Contaminants | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Camera and Photographic Equipment Repairers | Cutting and Slicing Machine Setters, Operators, and Tenders | Electrical and Electronic Equipment Assemblers | Etchers and Engravers | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Glass Blowers, Molders, Benders, and Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Opticians, Dispensing | Photonics Technicians | Timing Device Assemblers and Adjusters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Cut, grind, and polish eyeglasses, contact lenses, or other precision optical elements. Assemble and mount lenses into frames or process other optical elements. Includes precision lens polishers or grinders, centerer-edgers, and lens mounters.</t>
+  </si>
+  <si>
+    <t>Adjust lenses and frames to correct alignment. | Assemble eyeglass frames and attach shields, nose pads, and temple pieces, using pliers, screwdrivers, and drills. | Clean finished lenses and eyeglasses, using cloths and solvents. | Control equipment that coats lenses to alter their reflective qualities. | Examine prescriptions, work orders, or broken or used eyeglasses to determine specifications for lenses, contact lenses, or other optical elements. | Immerse eyeglass frames in solutions to harden, soften, or dye frames. | Inspect lens blanks to detect flaws, verify smoothness of surface, and ensure thickness of coating on lenses. | Inspect, weigh, and measure mounted or unmounted lenses after completion to verify alignment and conformance to specifications, using precision instruments. | Lay out lenses and trace lens outlines on glass, using templates. | Mount and secure lens blanks or optical lenses in holding tools or chucks of cutting, polishing, grinding, or coating machines. | Mount, secure, and align finished lenses in frames or optical assemblies, using precision hand tools. | Position and adjust cutting tools to specified curvature, dimensions, and depth of cut. | Remove lenses from molds and separate lenses in containers for further processing or storage. | Repair broken parts, using precision hand tools and soldering irons. | Select lens blanks, molds, tools, and polishing or grinding wheels, according to production specifications. | Set dials and start machines to polish lenses or hold lenses against rotating wheels to polish them manually. | Set up machines to polish, bevel, edge, or grind lenses, flats, blanks, or other precision optical elements. | Shape lenses appropriately so that they can be inserted into frames.</t>
+  </si>
+  <si>
+    <t>51-9111.00</t>
+  </si>
+  <si>
+    <t>Packaging and Filling Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Bundler | Closing Machine Operator | Computer Numerical Control Machine Operator (CNC Machine Operator) | Filler Operator | Machine Operator | Packaging Operator | Packing Attendant | Packing Machine Operator</t>
+  </si>
+  <si>
+    <t>Email software | Label printing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Public Safety and Security | Education and Training | English Language | Mathematics | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Control Precision | Manual Dexterity | Perceptual Speed | Problem Sensitivity | Oral Expression | Oral Comprehension | Selective Attention | Visualization | Flexibility of Closure | Information Ordering | Trunk Strength | Reaction Time | Rate Control | Multilimb Coordination | Finger Dexterity | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Pace Determined by Speed of Equipment | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Time Pressure | Importance of Being Exact or Accurate | Contact With Others | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Mixing and Blending Machine Setters, Operators, and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic | Packers and Packagers, Hand | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate or tend machines to prepare industrial or consumer products for storage or shipment. Includes cannery workers who pack food products.</t>
+  </si>
+  <si>
+    <t>Adjust machine components and machine tension and pressure according to size or processing angle of product. | Attach identification labels to finished packaged items, or cut stencils and stencil information on containers, such as lot numbers or shipping destinations. | Clean and remove damaged or otherwise inferior materials to prepare raw products for processing. | Clean packaging containers, line and pad crates, or assemble cartons to prepare for product packing. | Clean, oil, and make minor adjustments or repairs to machinery and equipment, such as opening valves or setting guides. | Count and record finished and rejected packaged items. | Inspect and remove defective products and packaging material. | Monitor the production line, watching for problems such as pile-ups, jams, or glue that isn't sticking properly. | Observe machine operations to ensure quality and conformity of filled or packaged products to standards. | Package the product in the form in which it will be sent out, for example, filling bags with flour from a chute or spout. | Regulate machine flow, speed, or temperature. | Remove finished packaged items from machine and separate rejected items. | Secure finished packaged items by hand tying, sewing, gluing, stapling, or attaching fastener. | Sort, grade, weigh, and inspect products, verifying and adjusting product weight or measurement to meet specifications. | Stack finished packaged items, or wrap protective material around each item, and pack the items in cartons or containers. | Start machine by engaging controls. | Stock and sort product for packaging or filling machine operation, and replenish packaging supplies, such as wrapping paper, plastic sheet, boxes, cartons, glue, ink, or labels. | Stop or reset machines when malfunctions occur, clear machine jams, and report malfunctions to a supervisor. | Supply materials to spindles, conveyors, hoppers, or other feeding devices and unload packaged product. | Tend or operate machine that packages product.</t>
+  </si>
+  <si>
+    <t>51-9123.00</t>
+  </si>
+  <si>
+    <t>Painting, Coating, and Decorating Workers</t>
+  </si>
+  <si>
+    <t>Decaler | Decorator | Glass Decorator | Glazer | In Mold Coater | Painter | Pottery Decorator | Silk-Screen Operator | Spray Painter | Sprayer</t>
+  </si>
+  <si>
+    <t>Adobe FreeHand MX | Adobe Illustrator | Adobe Photoshop | Corel WordPerfect Office Suite | Microsoft Excel</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Visual Color Discrimination | Manual Dexterity | Finger Dexterity | Problem Sensitivity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Etchers and Engravers | Foundry Mold and Coremakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Patternmakers, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Paint, coat, or decorate articles, such as furniture, glass, plateware, pottery, jewelry, toys, books, or leather.</t>
+  </si>
+  <si>
+    <t>Apply coatings, such as paint, ink, or lacquer, to protect or decorate workpiece surfaces, using spray guns, pens, or brushes. | Clean and maintain tools and equipment, using solvents, brushes, and rags. | Clean surfaces of workpieces in preparation for coating, using cleaning fluids, solvents, brushes, scrapers, steam, sandpaper, or cloth. | Conceal blemishes in workpieces, such as nicks and dents, using fillers such as putty. | Examine finished surfaces of workpieces to verify conformance to specifications and retouch any defective areas. | Place coated workpieces in ovens or dryers for specified times to dry or harden finishes. | Read job orders and inspect workpieces to determine work procedures and materials required. | Rinse, drain, or wipe coated workpieces to remove excess coating material or to facilitate setting of finish coats on workpieces. | Select and mix ingredients to prepare coating substances according to specifications, using paddles or mechanical mixers.</t>
+  </si>
+  <si>
+    <t>51-9124.00</t>
+  </si>
+  <si>
+    <t>Coating, Painting, and Spraying Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Automotive Painter (Auto Painter) | Automotive Refinish Technician (Auto Refinish Tech) | Coater Operator | Hand Sprayer | Industrial Painter | Paint Technician (Paint Tech) | Painter | Powder Coater | Spray Painter | Top Coater</t>
+  </si>
+  <si>
+    <t>Inventory control software | Inventory management systems | Maintenance management software | Materials requirement planning MRP software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Robotic painting software | Scheduling software | Time recording software</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Chemistry | Mechanical | English Language | Mathematics | Public Safety and Security | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Control Precision | Visual Color Discrimination | Manual Dexterity | Finger Dexterity | Far Vision | Trunk Strength | Visualization | Perceptual Speed | Flexibility of Closure | Information Ordering | Deductive Reasoning | Problem Sensitivity | Oral Comprehension | Extent Flexibility | Dynamic Strength | Multilimb Coordination | Selective Attention</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Making Repetitive Motions | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Spend Time Standing | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Walking or Running | Freedom to Make Decisions | Physical Proximity | Health and Safety of Other Workers | Exposed to Hazardous Conditions | Contact With Others</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Automotive Body and Related Repairers | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Fiberglass Laminators and Fabricators | Furniture Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Laundry and Dry-Cleaning Workers | Maintenance Workers, Machinery | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Bleaching and Dyeing Machine Operators and Tenders | Tire Builders</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend spraying or rolling machines to coat or paint any of a wide variety of products, including glassware, cloth, ceramics, metal, plastic, paper, or wood, with lacquer, silver, copper, rubber, varnish, glaze, enamel, oil, or rust-proofing materials. Includes painters of transportation vehicles such as painters in auto body repair facilities.</t>
+  </si>
+  <si>
+    <t>Adjust controls on infrared ovens, heat lamps, portable ventilators, or exhaust units to speed the drying of surfaces between coats. | Apply primer over any repairs made to surfaces. | Apply rust-resistant undercoats and caulk and seal seams. | Attach hoses or nozzles to machines, using wrenches and pliers, and make adjustments to obtain the proper dispersion of spray. | Buff and wax the finished paintwork. | Clean equipment and work areas. | Determine paint flow, viscosity, and coating quality by performing visual inspections, or by using viscometers. | Disassemble, clean, and reassemble sprayers or power equipment, using solvents, wire brushes, and cloths. | Dispose of hazardous waste in an appropriate manner. | Examine, measure, weigh, or test sample products to ensure conformance to specifications. | Fill hoppers, reservoirs, troughs, or pans with material used to coat, paint, or spray, using conveyors or pails. | Fill small dents or scratches with body fillers and smooth surfaces to prepare for painting. | Hold or position spray guns to direct spray onto articles. | Mix paints to match color specifications or original colors, stirring or thinning paints, using spatulas or power mixing equipment. | Monitor painting operations to identify flaws, such as blisters or streaks, and correct their causes. | Observe machine gauges and equipment operation to detect defects or deviations from standards, and make adjustments as necessary. | Operate auxiliary machines or equipment used in coating or painting processes. | Operate lifting or moving devices to move equipment or materials to access areas to be painted. | Record operational data on specified forms. | Remove grease, dirt, paint, or rust from surfaces in preparation for paint application, using abrasives, solvents, brushes, blowtorches, washing tanks, or sandblasters. | Remove materials, parts, or workpieces from painting or coating machines, using hand tools. | Sand and apply sealer to properly dried finish. | Set up portable equipment, such as ventilators, exhaust units, ladders, or scaffolding. | Spray prepared surfaces with specified amounts of primers and decorative or finish coatings. | Start and stop operation of machines, using levers or buttons. | Thread or feed items or products through or around machine rollers and dryers. | Turn dials, handwheels, valves, or switches to regulate conveyor speeds, machine temperature, air pressure and circulation, and the flow or spray of coatings or paints. | Use brush to hand-paint areas in need of retouching or unreachable with a spray gun. | Weigh or measure chemicals, coatings, or paints before adding them to machines.</t>
+  </si>
+  <si>
+    <t>51-9141.00</t>
+  </si>
+  <si>
+    <t>Semiconductor Processing Technicians</t>
+  </si>
+  <si>
+    <t>Device Processing Engineer | Diffusion Operator | Manufacture Specialist | Manufacturing Technician | Metalorganic Chemical Vapor Deposition Engineer (MOCVD Engineer) | Probe Operator | Process Technician | Wafer Fabrication Operator</t>
+  </si>
+  <si>
+    <t>Camstar Systems Camstar Semiconductor Suite | Database software | Eyelit Manufacturing | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | National Instruments TestStand | Python | SAP software | yieldWerx</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language | Public Safety and Security | Computers and Electronics | Education and Training | Chemistry</t>
+  </si>
+  <si>
+    <t>Near Vision | Written Comprehension | Arm-Hand Steadiness | Oral Comprehension | Inductive Reasoning | Finger Dexterity | Control Precision | Oral Expression | Deductive Reasoning | Problem Sensitivity | Written Expression | Multilimb Coordination | Manual Dexterity | Information Ordering | Visualization | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Exposed to Contaminants | Work With or Contribute to a Work Group or Team | Consequence of Error | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Importance of Repeating Same Tasks | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Computer Numerically Controlled Tool Operators | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Microsystems Engineers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Ophthalmic Laboratory Technicians | Photonics Technicians | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Perform any or all of the following functions in the manufacture of electronic semiconductors: load semiconductor material into furnace; saw formed ingots into segments; load individual segment into crystal growing chamber and monitor controls; locate crystal axis in ingot using x-ray equipment and saw ingots into wafers; and clean, polish, and load wafers into series of special purpose furnaces, chemical baths, and equipment used to form circuitry and change conductive properties.</t>
+  </si>
+  <si>
+    <t>Align photo mask pattern on photoresist layer, expose pattern to ultraviolet light, and develop pattern, using specialized equipment. | Calculate etching time based on thickness of material to be removed from wafers or crystals. | Clean and maintain equipment, including replacing etching and rinsing solutions and cleaning bath containers and work area. | Clean semiconductor wafers using cleaning equipment, such as chemical baths, automatic wafer cleaners, or blow-off wands. | Connect reactor to computer, using hand tools and power tools. | Count, sort, and weigh processed items. | Etch, lap, polish, or grind wafers or ingots to form circuitry and change conductive properties, using etching, lapping, polishing, or grinding equipment. | Inspect equipment for leaks, diagnose malfunctions, and request repairs. | Inspect materials, components, or products for surface defects and measure circuitry, using electronic test equipment, precision measuring instruments, microscope, and standard procedures. | Load and unload equipment chambers and transport finished product to storage or to area for further processing. | Load semiconductor material into furnace. | Maintain processing, production, and inspection information and reports. | Manipulate valves, switches, and buttons, or key commands into control panels to start semiconductor processing cycles. | Measure and weigh amounts of crystal growing materials, mix and grind materials, load materials into container, and monitor processing procedures to help identify crystal growing problems. | Monitor operation and adjust controls of processing machines and equipment to produce compositions with specific electronic properties, using computer terminals. | Place semiconductor wafers in processing containers or equipment holders, using vacuum wand or tweezers. | Scribe or separate wafers into dice. | Set, adjust, and readjust computerized or mechanical equipment controls to regulate power level, temperature, vacuum, and rotation speed of furnace, according to crystal growing specifications. | Stamp, etch, or scribe identifying information on finished component according to specifications. | Study work orders, instructions, formulas, and processing charts to determine specifications and sequence of operations.</t>
+  </si>
+  <si>
+    <t>51-9151.00</t>
+  </si>
+  <si>
+    <t>Photographic Process Workers and Processing Machine Operators</t>
+  </si>
+  <si>
+    <t>Digital Printer Operator | Film Processor | Film Technician | Lab Technician | Photo Lab Specialist | Photo Lab Technician (Photographic Laboratory Technician) | Photo Printer | Photo Specialist | Photo Technician</t>
+  </si>
+  <si>
+    <t>Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Amazon Web Services AWS software | Camera Bits Photo Mechanic | Cascading style sheets CSS | Docker | ExpressDigital Labtricity | Git | HeliconSoft Helicon Focus | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | MongoDB | MySQL | Phase One Capture One | RESTful API | SAP software | Structured query language SQL | TypeScript</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Computers and Electronics | Production and Processing | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Visual Color Discrimination | Oral Comprehension | Oral Expression | Written Comprehension | Deductive Reasoning | Information Ordering | Flexibility of Closure | Selective Attention | Arm-Hand Steadiness | Control Precision | Speech Clarity | Manual Dexterity | Visualization | Perceptual Speed | Inductive Reasoning | Problem Sensitivity | Written Expression | Speech Recognition | Finger Dexterity | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Time Pressure | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Calibration Technologists and Technicians | Camera and Photographic Equipment Repairers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Computer, Automated Teller, and Office Machine Repairers | Etchers and Engravers | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Inspectors, Testers, Sorters, Samplers, and Weighers | Motion Picture Projectionists | Office Machine Operators, Except Computer | Painting, Coating, and Decorating Workers | Paper Goods Machine Setters, Operators, and Tenders | Patternmakers, Metal and Plastic | Photographers | Photonics Technicians | Prepress Technicians and Workers | Print Binding and Finishing Workers | Printing Press Operators | Semiconductor Processing Technicians | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Perform work involved in developing and processing photographic images from film or digital media. May perform precision tasks such as editing photographic negatives and prints.</t>
+  </si>
+  <si>
+    <t>Clean or maintain photoprocessing or darkroom equipment, using ultrasonic equipment or cleaning and rinsing solutions. | Create prints according to customer specifications and laboratory protocols. | Examine developed prints for defects, such as broken lines, spots, or blurs. | Examine drawings, negatives, or photographic prints to determine coloring, shading, accenting, or other changes required for retouching or restoration. | Examine quality of film fades or dissolves for potential color corrections, using color analyzers. | Fill tanks of processing machines with solutions such as developer, dyes, stop-baths, fixers, bleaches, or washes. | Immerse film, negatives, paper, or prints in developing solutions, fixing solutions, and water to complete photographic development processes. | Insert processed negatives and prints into envelopes for delivery to customers. | Load circuit boards, racks or rolls of film, negatives, or printing paper into processing or printing machines. | Load digital images onto computers directly from cameras or from storage devices, such as flash memory cards or universal serial bus (USB) devices. | Maintain records, such as quantities or types of processing completed, materials used, or customer charges. | Measure and mix chemicals to prepare solutions for processing, according to formulas. | Monitor equipment operation to detect malfunctions. | Operate scanners or related computer equipment to digitize negatives, photographic prints, or other images. | Operate special equipment to perform tasks such as transferring film to videotape or producing photographic enlargements. | Place sensitized paper in frames of projection printers, photostats, or other reproduction machines. | Produce color or black-and-white photographs, negatives, or slides, applying standard photographic reproduction techniques and procedures. | Produce timed prints with separate densities or color settings for each scene of a production. | Read work orders to determine required processes, techniques, materials, or equipment. | Reprint originals for enlargement or in sections to be pieced together. | Retouch photographic negatives or original prints to correct defects. | Review computer-processed digital images for quality. | Select digital images for printing, specify number of images to be printed, and direct to printer, using computer software. | Set or adjust machine controls, according to specifications, type of operation, or material requirements. | Splice broken or separated film and mount film on reels. | Thread filmstrips through densitometers or sensitometers and expose film to light to determine density of film, necessary color corrections, or light sensitivity. | Upload digital images onto Web sites for customers.</t>
+  </si>
+  <si>
+    <t>51-9161.00</t>
+  </si>
+  <si>
+    <t>Computer Numerically Controlled Tool Operators</t>
+  </si>
+  <si>
+    <t>CNC Gear Operator (Computer Numerical Control Gear Operator) | CNC Lathe Operator (Computer Numerical Control Lathe Operator) | CNC Machine Operator (Computer Numerical Control Machine Operator) | CNC Machinist (Computer Numerical Control Machinist) | CNC Mill Operator (Computer Numerical Control Mill Operator) | CNC Operator (Computer Numerical Control Operator) | CNC Set Up Operator (Computer Numerical Control Set Up Operator) | Machine Operator | Machine Set Up Operator</t>
+  </si>
+  <si>
+    <t>1CadCam Unigraphics | Autodesk AutoCAD | BobCAD-CAM | CGTech Vericut CNC | CNC Consulting Machinists' Calculator | CNC Mastercam | Cadem CAPSMill | Cadem CAPSTurn | Cadem NCnet | Cadem seeNC Mill | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam PowerMILL | Direct motion computer numerically controlled CNC software | ERP software | EZ-CAM | EditCNC | Eko | ExtraTech Machine Tools Suite | FaceTime | FlashCut CNC | G-code | HOMAG WoodWOP | IMSI TurboCAD | JETCAM | KCD cabinet design software | Kentech Kipware M CNC | Kentech Kipware Studio | Kentech Kipware T CNC | Kentech Kipware Trig Kalculator | Kentech Kipware X CNC | Kentech PROTALK | Kentech machine shop software | M-code | MDSI OpenCNC | MUMPS M | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | PTC Creo Parametric | PartMaker SwissCAM | Predator DNC | SAP software | SigmaTEK SigmaNEST | SmartCAMcnc SmartCAM | Supervisory control and data acquisition SCADA software | TekSoft CAMWorks | UGS Solid Edge | Vero International VISI-Series | Vero Software Edgecam | Vero Software SURFCAM | Virtual Gibbs CADD/CAM | Work inspection software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Mathematics | Production and Processing | Mechanical | English Language | Engineering and Technology | Education and Training | Design | Administration and Management</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Problem Sensitivity | Information Ordering | Reaction Time | Control Precision | Hearing Sensitivity | Oral Comprehension | Perceptual Speed | Visualization | Manual Dexterity | Finger Dexterity | Auditory Attention | Trunk Strength | Rate Control | Multilimb Coordination | Selective Attention | Flexibility of Closure | Category Flexibility | Deductive Reasoning | Written Comprehension | Inductive Reasoning | Oral Expression | Speech Clarity | Speech Recognition | Depth Perception | Visual Color Discrimination | Speed of Closure | Number Facility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Standing | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Hazardous Equipment | Freedom to Make Decisions | Contact With Others | Importance of Repeating Same Tasks | Pace Determined by Speed of Equipment | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Computer Numerically Controlled Tool Programmers | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Robotics Technicians | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate computer-controlled tools, machines, or robots to machine or process parts, tools, or other work pieces made of metal, plastic, wood, stone, or other materials. May also set up and maintain equipment.</t>
+  </si>
+  <si>
+    <t>Adjust machine feed and speed, change cutting tools, or adjust machine controls when automatic programming is faulty or if machines malfunction. | Calculate machine speed and feed ratios and the size and position of cuts. | Check to ensure that workpieces are properly lubricated and cooled during machine operation. | Clean machines, tooling, or parts, using solvents or solutions and rags. | Confer with supervisors or programmers to resolve machine malfunctions or production errors or to obtain approval to continue production. | Control coolant systems. | Enter commands or load control media, such as tapes, cards, or disks, into machine controllers to retrieve programmed instructions. | Examine electronic components for defects or completeness of laser-beam trimming, using microscopes. | Implement changes to machine programs, and enter new specifications, using computers. | Input initial part dimensions into machine control panels. | Insert control instructions into machine control units to start operation. | Lay out and mark areas of parts to be shot peened and fill hoppers with shot. | Lift workpieces to machines manually or with hoists or cranes. | Listen to machines during operation to detect sounds such as those made by dull cutting tools or excessive vibration, and adjust machines to compensate for problems. | Maintain machines and remove and replace broken or worn machine tools, using hand tools. | Measure dimensions of finished workpieces to ensure conformance to specifications, using precision measuring instruments, templates, and fixtures. | Modify cutting programs to account for problems encountered during operation, and save modified programs. | Monitor machine operation and control panel displays, and compare readings to specifications to detect malfunctions. | Mount, install, align, and secure tools, attachments, fixtures, and workpieces on machines, using hand tools and precision measuring instruments. | Remove and replace dull cutting tools. | Review program specifications or blueprints to determine and set machine operations and sequencing, finished workpiece dimensions, or numerical control sequences. | Set up and operate computer-controlled machines or robots to perform one or more machine functions on metal or plastic workpieces. | Set up future jobs while machines are operating. | Stack or load finished items, or place items on conveyor systems. | Stop machines to remove finished workpieces or to change tooling, setup, or workpiece placement, according to required machining sequences. | Transfer commands from servers to computer numerical control (CNC) modules, using computer network links. | Write simple programs for computer-controlled machine tools.</t>
+  </si>
+  <si>
+    <t>51-9162.00</t>
+  </si>
+  <si>
+    <t>Computer Numerically Controlled Tool Programmers</t>
+  </si>
+  <si>
+    <t>CAD Programmer (Computer-Aided Design Programmer) | CAM Programmer (Computer-Aided Manufacturing Programmer) | CNC Machine Operator (Computer Numerical Control Machine Operator) | CNC Machinist (Computer Numerical Control Machinist) | CNC Operator (Computer Numerical Control Operator) | CNC Programmer (Computer Numerical Control Programmer) | CNC Tech (Computer Numerical Control Technician) | CNC Tool Programmer (Computer Numerical Control Tool Programmer) | Numerical Control Programmer (NC Programmer) | Programmer</t>
+  </si>
+  <si>
+    <t>1CadCam Unigraphics | 3D Systems GibbsCAM | Aptean Made2Manage | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk PartMaker | Autodesk PowerMill | Autodesk PowerShape | BobCAD-CAM | CGTech Vericut CNC | Celeritive Technologies VoluMill | Cimatron CimatronE | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam FeatureCAM | Delcam PartMaker | Dolphin CAD/CAM | Extensible markup language XML | FANUC CNC | FaceTime | FastCAM | G-code | GO2cam | GeoPath CAD/CAM System | Geometric Technologies CAMWorks | Gerber Technology CutWorks | GibbsCAM | Hypertherm ProNest | ICAM CAM-POST | Intelitek spectraCAM Milling | Intelitek spectraCAM Turning | Kubotek KeyCreator Machinist | LAB SUM3D | M-code | MachineWorks Ltd. MachineWorks | Manusoft Technologies IMOLD | Mastercam computer-aided design and manufacturing software | MecSoft Corporation RhinoCAM | MecSoft Corporation VisualMILL | MecSoft Corporation VisualTURN | Metalcam Fikus Visualcam | Metalix CAD/CAM System cncKad | Metamation MetaCAM | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Missler Software TopSolid | Open Mind Software hyperMILL | PTC Creo Parametric | Post-processor software | RADAN Radbend | SAP software | SharpCam Ltd. SharpCam | Siemens NX | Siemens Teamcenter | Simulation software | SmartCAMcnc SmartCAM | SolidCAM CAM software | SolidCAM iMachining | Sprut Technology SprutCAM | Tebis computer aided design software | Technos Astra R-Nesting | Technos Astra S-Nesting | Top Systems T-FLEX CAM | Uncamco Ucam | Vero Software ALPHACAM Milling | Vero Software ALPHACAM Turning | Vero Software Edgecam | Vero Software PEPS | Vero Software RADAN | Vero Software SMIRTsoftware | Vero Software SURFCAM | Vero Software VISI | Vero Software WorkNC | Vero Software machining STRATEGIST</t>
+  </si>
+  <si>
+    <t>Monitoring | Mathematics | Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Engineering and Technology | Mathematics | Design | Computers and Electronics | English Language | Education and Training | Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Information Ordering | Perceptual Speed | Mathematical Reasoning | Selective Attention | Visualization | Category Flexibility | Written Comprehension | Oral Comprehension | Arm-Hand Steadiness | Number Facility | Inductive Reasoning | Deductive Reasoning | Written Expression | Oral Expression | Speech Clarity | Speech Recognition | Control Precision | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Frequency of Decision Making | Time Pressure | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | E-Mail | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | Freedom to Make Decisions | Indoors, Environmentally Controlled | Pace Determined by Speed of Equipment | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Calibration Technologists and Technicians | Computer Hardware Engineers | Computer Numerically Controlled Tool Operators | Computer Programmers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machinists | Mechanical Drafters | Mechanical Engineering Technologists and Technicians | Mechatronics Engineers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Patternmakers, Metal and Plastic | Robotics Engineers | Robotics Technicians</t>
+  </si>
+  <si>
+    <t>Develop programs to control machining or processing of materials by automatic machine tools, equipment, or systems. May also set up, operate, or maintain equipment.</t>
+  </si>
+  <si>
+    <t>Align and secure pattern film on reference tables of optical programmers, and observe enlarger scope views of printed circuit boards. | Analyze job orders, drawings, blueprints, specifications, printed circuit board pattern films, and design data to calculate dimensions, tool selection, machine speeds, and feed rates. | Compare encoded tapes or computer printouts with original part specifications and blueprints to verify accuracy of instructions. | Determine reference points, machine cutting paths, or hole locations, and compute angular and linear dimensions, radii, and curvatures. | Determine the sequence of machine operations, and select the proper cutting tools needed to machine workpieces into the desired shapes. | Enter computer commands to store or retrieve parts patterns, graphic displays, or programs that transfer data to other media. | Enter coordinates of hole locations into program memories by depressing pedals or buttons of programmers. | Modify existing programs to enhance efficiency. | Observe machines on trial runs or conduct computer simulations to ensure that programs and machinery will function properly and produce items that meet specifications. | Order tooling for jobs. | Perform preventative maintenance or minor repairs on machines. | Prepare geometric layouts from graphic displays, using computer-assisted drafting software or drafting instruments and graph paper. | Revise programs or tapes to eliminate errors, and retest programs to check that problems have been solved. | Sort shop orders into groups to maximize materials utilization and minimize machine setup time. | Write instruction sheets and cutter lists for a machine's controller to guide setup and encode numerical control tapes. | Write programs in the language of a machine's controller and store programs on media, such as punch tapes, magnetic tapes, or disks.</t>
+  </si>
+  <si>
+    <t>51-9191.00</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Coater Operator | Glue Line Operator | Glue Reel Operator | Gluer Machine Operator | Gluing Pressman | Machine Operator | Perfect Bind Machine Operator | Sealer Operator | Utility Worker</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Static Strength | Arm-Hand Steadiness | Near Vision | Trunk Strength | Control Precision | Problem Sensitivity | Rate Control | Finger Dexterity | Perceptual Speed | Multilimb Coordination | Reaction Time | Extent Flexibility | Oral Comprehension | Stamina | Selective Attention | Visualization | Category Flexibility | Information Ordering | Deductive Reasoning | Oral Expression | Written Comprehension | Speech Recognition | Auditory Attention | Depth Perception | Dynamic Strength | Flexibility of Closure | Inductive Reasoning | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Spend Time Standing | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Time Pressure | Pace Determined by Speed of Equipment | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Consequence of Error | Spend Time Walking or Running | Physical Proximity | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate or tend bonding machines that use adhesives to join items for further processing or to form a completed product. Processes include joining veneer sheets into plywood; gluing paper; or joining rubber and rubberized fabric parts, plastic, simulated leather, or other materials.</t>
+  </si>
+  <si>
+    <t>Adjust machine components according to specifications such as widths, lengths, and thickness of materials and amounts of glue, cement, or adhesive required. | Align and position materials being joined to ensure accurate application of adhesive or heat sealing. | Clean and maintain gluing and cementing machines, using solutions, lubricants, brushes, and scrapers. | Examine and measure completed materials or products to verify conformance to specifications, using measuring devices such as tape measures, gauges, or calipers. | Fill machines with glue, cement, or adhesives. | Maintain production records such as quantities, dimensions, and thicknesses of materials processed. | Measure and mix ingredients to prepare glue. | Monitor machine operations to detect malfunctions and report or resolve problems. | Mount or load material such as paper, plastic, wood, or rubber in feeding mechanisms of cementing or gluing machines. | Observe gauges, meters, and control panels to obtain information about equipment temperatures and pressures, or the speed of feeders or conveyors. | Perform test production runs and make adjustments as necessary to ensure that completed products meet standards and specifications. | Read work orders and communicate with coworkers to determine machine and equipment settings and adjustments and supply and product specifications. | Remove and stack completed materials or products, and restock materials to be joined. | Remove jammed materials from machines and readjust components as necessary to resume normal operations. | Start machines, and turn valves or move controls to feed, admit, apply, or transfer materials and adhesives, and to adjust temperature, pressure, and time settings. | Transport materials, supplies, and finished products between storage and work areas, using forklifts.</t>
+  </si>
+  <si>
+    <t>51-9192.00</t>
+  </si>
+  <si>
+    <t>Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Anodizer | Clean in Places Operator (CIP Operator) | Filler Operator | Parts Cleaner | Sanitation Technician | Sanitation Worker | Sanitizer | Tub Wash Operator | Tub Washer | Wash Crew Person</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Arm-Hand Steadiness | Perceptual Speed | Information Ordering | Trunk Strength | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Walking or Running | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Cleaners of Vehicles and Equipment | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Cooking Machine Operators and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend machines to wash or clean products, such as barrels or kegs, glass items, tin plate, food, pulp, coal, plastic, or rubber, to remove impurities.</t>
+  </si>
+  <si>
+    <t>Add specified amounts of chemicals to equipment at required times to maintain solution levels and concentrations. | Adjust, clean, and lubricate mechanical parts of machines, using hand tools and grease guns. | Drain, clean, and refill machines or tanks at designated intervals, using cleaning solutions or water. | Draw samples for laboratory analysis, or test solutions for conformance to specifications, such as acidity or specific gravity. | Examine and inspect machines to detect malfunctions. | Load machines with objects to be processed and unload them after cleaning, placing them on conveyors or racks. | Measure, weigh, or mix cleaning solutions, using measuring tanks, calibrated rods or suction tubes. | Observe machine operations, gauges, or thermometers, and adjust controls to maintain specified conditions. | Operate or tend machines to wash and remove impurities from items such as barrels or kegs, glass products, tin plate surfaces, dried fruit, pulp, animal stock, coal, manufactured articles, plastic, or rubber. | Record gauge readings, materials used, processing times, or test results in production logs. | Set controls to regulate temperature and length of cycles, and start conveyors, pumps, agitators, and machines.</t>
+  </si>
+  <si>
+    <t>51-9193.00</t>
+  </si>
+  <si>
+    <t>Cooling and Freezing Equipment Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Certified Refrigeration Operator | Compressor Operator | Engine Room Operator | Freezer Operator | Freezer Person | Ice Cream Maker | Machine Operator | Refrigeration Operator | Refrigeration Technician</t>
+  </si>
+  <si>
+    <t>Google Gmail | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Learning | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | English Language | Food Production | Administration and Management | Mathematics | Public Safety and Security | Education and Training</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Deductive Reasoning | Perceptual Speed | Arm-Hand Steadiness | Trunk Strength | Static Strength | Reaction Time | Control Precision | Finger Dexterity | Manual Dexterity | Oral Expression | Speech Clarity | Speech Recognition | Rate Control | Multilimb Coordination | Category Flexibility | Information Ordering | Inductive Reasoning | Written Expression | Written Comprehension | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Environmentally Controlled | Spend Time Standing | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Time Pressure | Exposed to Very Hot or Cold Temperatures | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Frequency of Decision Making | Pace Determined by Speed of Equipment | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Written Letters and Memos | Exposed to Hazardous Equipment | Exposed to Contaminants | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Operate or tend equipment such as cooling and freezing units, refrigerators, batch freezers, and freezing tunnels, to cool or freeze products, food, blood plasma, and chemicals.</t>
+  </si>
+  <si>
+    <t>Activate mechanical rakes to regulate flow of ice from storage bins to vats. | Adjust machine or freezer speed and air intake to obtain desired consistency and amount of product. | Assemble equipment, and attach pipes, fittings, or valves, using hand tools. | Correct machinery malfunctions by performing actions such as removing jams, and inform supervisors of malfunctions as necessary. | Insert forming fixtures, and start machines that cut frozen products into measured portions or specified shapes. | Inspect and flush lines with solutions or steam, and spray equipment with sterilizing solutions. | Load and position wrapping paper, sticks, bags, or cartons into dispensing machines. | Measure or weigh specified amounts of ingredients or materials, and load them into tanks, vats, hoppers, or other equipment. | Monitor pressure gauges, ammeters, flowmeters, thermometers, or products, and adjust controls to maintain specified conditions, such as feed rate, product consistency, temperature, air pressure, and machine speed. | Place or position containers into equipment, and remove containers after completion of cooling or freezing processes. | Read dials and gauges on panel control boards to ascertain temperatures, alkalinities, and densities of mixtures, and turn valves to obtain specified mixtures. | Record temperatures, amounts of materials processed, or test results on report forms. | Sample and test product characteristics such as specific gravity, acidity, and sugar content, using hydrometers, pH meters, or refractometers. | Scrape, dislodge, or break excess frost, ice, or frozen product from equipment to prevent accumulation, using hands and hand tools. | Start agitators to blend contents, or start beater, scraper, and expeller blades to mix contents with air and prevent sticking. | Start machinery, such as pumps, feeders, or conveyors, and turn valves to heat, admit, or transfer products, refrigerants, or mixes. | Stir material with spoons or paddles to mix ingredients or allow even cooling and prevent coagulation. | Weigh packages and adjust freezer air valves or switches on filler heads to obtain specified amounts of product in each container.</t>
+  </si>
+  <si>
+    <t>51-9194.00</t>
+  </si>
+  <si>
+    <t>Etchers and Engravers</t>
+  </si>
+  <si>
+    <t>Acid Etch Operator | Award Machine Operator | Chemical Engraver | Electronic Engraver | Engraver | Etcher | Laser Engraver | Photo Engraver | Screen Making Technician | Wet Process Technician</t>
+  </si>
+  <si>
+    <t>Adobe Illustrator | Computer aided design and computer aided manufacturing CAD/CAM engraving software | Corel CorelDraw Graphics Suite | Delcam ArtCAM Express | Gravograph GravoStyle | Microsoft Office software | Microsoft Windows | Western Engravers Supply Vision EXPERT</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Customer and Personal Service | Mechanical | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Control Precision | Oral Comprehension | Oral Expression | Selective Attention | Manual Dexterity | Finger Dexterity | Speech Clarity | Speech Recognition | Visualization | Problem Sensitivity | Written Comprehension | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Exposed to Contaminants | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Fabric and Apparel Patternmakers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Jewelers and Precious Stone and Metal Workers | Layout Workers, Metal and Plastic | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Ophthalmic Laboratory Technicians | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Prepress Technicians and Workers | Printing Press Operators | Stone Cutters and Carvers, Manufacturing | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Engrave or etch metal, wood, rubber, or other materials. Includes such workers as etcher-circuit processors, pantograph engravers, and silk screen etchers.</t>
+  </si>
+  <si>
+    <t>Adjust depths and sizes of cuts by adjusting heights of worktables, or by adjusting machine-arm gauges. | Brush or wipe acid over engraving to darken or highlight inscriptions. | Clean and polish engraved areas. | Determine machine settings, and move bars or levers to reproduce designs on rollers or plates. | Engrave and print patterns, designs, etchings, trademarks, or lettering onto flat or curved surfaces of a wide variety of metal, glass, plastic, or paper items, using hand tools or hand-held power tools. | Examine engraving for quality of cut, burrs, rough spots, and irregular or incomplete engraving. | Examine sketches, diagrams, samples, blueprints, or photographs to decide how designs are to be etched, cut, or engraved onto workpieces. | Expose workpieces to acid to develop etch patterns such as designs, lettering, or figures. | Fill etched characters with opaque paste to improve readability. | Guide stylus over template, causing cutting tool to duplicate design or letters on workpiece. | Insert cutting tools or bits into machines and secure them with wrenches. | Inspect etched work for depth of etching, uniformity, and defects, using calibrated microscopes, gauges, fingers, or magnifying lenses. | Measure and compute dimensions of lettering, designs, or patterns to be engraved. | Neutralize workpieces to remove acid, wax, or enamel, using water, solvents, brushes, or specialized machines. | Position and clamp workpieces, plates, or rollers in holding fixtures. | Prepare etching chemicals according to formulas, diluting acid with water to obtain solutions of specified concentration. | Prepare workpieces for etching or engraving by cutting, sanding, cleaning, polishing, or treating them with wax, acid resist, lime, etching powder, or light-sensitive enamel. | Print proofs or examine designs to verify accuracy of engraving, and rework engraving as required. | Remove completed workpieces and place them in trays. | Remove wax or tape from etched glassware by using a stylus or knife, or by immersing ware in hot water. | Sandblast exposed areas of glass to cut designs in surfaces, using spray guns. | Set reduction scales to attain specified sizes of reproduction on workpieces, and set pantograph controls for required heights, depths, and widths of cuts. | Sketch, trace, or scribe layout lines and designs on workpieces, plates, dies, or rollers, using compasses, scribers, gravers, or pencils. | Start machines and lower cutting tools to beginning points on patterns. | Transfer image to workpiece, using contact printer, pantograph stylus, silkscreen printing device, or stamp pad. | Use computer software to design patterns for engraving.</t>
+  </si>
+  <si>
+    <t>51-9195.00</t>
+  </si>
+  <si>
+    <t>Molders, Shapers, and Casters, Except Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Bed Laborer | Caster | Injection Molding Machine Operator | Machine Operator | Mold Mechanic | Molder | Molding Line Operator | Press Operator</t>
+  </si>
+  <si>
+    <t>Dassault Systemes SolidWorks | Inventory control software | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Timekeeping software</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Near Vision | Multilimb Coordination | Selective Attention | Oral Comprehension | Extent Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Time Pressure | Work With or Contribute to a Work Group or Team | Indoors, Not Environmentally Controlled | Contact With Others | Spend Time Walking or Running | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Exposed to Contaminants | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Bending or Twisting Your Body | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Fiberglass Laminators and Fabricators | Foundry Mold and Coremakers | Glass Blowers, Molders, Benders, and Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Potters, Manufacturing | Refractory Materials Repairers, Except Brickmasons | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tire Builders | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Mold, shape, form, cast, or carve products such as food products, figurines, tile, pipes, and candles consisting of clay, glass, plaster, concrete, stone, or combinations of materials.</t>
+  </si>
+  <si>
+    <t>Align and assemble parts to produce completed products, using gauges and hand tools. | Assemble, insert, and adjust wires, tubes, cores, fittings, rods, or patterns into molds, using hand tools and depth gauges. | Bore holes or cut grates, risers, or pouring spouts in molds, using power tools. | Brush or spray mold surfaces with parting agents or insert paper into molds to ensure smoothness and prevent sticking or seepage. | Clean, finish, and lubricate molds and mold parts. | Construct or form molds for use in casting clay or plaster objects, using plaster, fiberglass, rubber, casting machines, patterns, or flasks. | Engrave or stamp identifying symbols, letters, or numbers on products. | Load or stack filled molds in ovens, dryers, or curing boxes, or on storage racks or carts. | Measure and cut products to specified dimensions, using measuring and cutting instruments. | Measure ingredients and mix molding, casting material, or sealing compounds to prescribed consistencies, according to formulas. | Operate and adjust controls of heating equipment to melt material or to cure, dry, or bake filled molds. | Patch broken edges or fractures, using clay or plaster. | Pour, pack, spread, or press plaster, concrete, or other materials into or around models or molds. | Read work orders or examine parts to determine parts or sections of products to be produced. | Remove excess materials and level and smooth wet mold mixtures. | Repair mold defects, such as cracks or broken edges, using patterns, mold boxes, or hand tools. | Select sizes and types of molds according to instructions. | Separate models or patterns from molds and examine products for accuracy. | Set the proper operating temperature for each casting. | Smooth surfaces of molds, using scraping tools or sandpaper. | Tap or tilt molds to ensure uniform distribution of materials. | Trim or remove excess material, using scrapers, knives, or band saws. | Verify dimensions of products, using measuring instruments, such as calipers, vernier gauges, or protractors. | Withdraw cores or other loose mold members after castings solidify.</t>
+  </si>
+  <si>
+    <t>51-9195.03</t>
+  </si>
+  <si>
+    <t>Stone Cutters and Carvers, Manufacturing</t>
+  </si>
+  <si>
+    <t>Carver | Cutter | Granite Cutter | Polisher | Sandblast Carver | Sandblaster | Stone Carver | Stone Cutter | Stone Fabricator</t>
+  </si>
+  <si>
+    <t>Corel Paint Shop Pro | Inventory control software | Microsoft Excel | Microsoft Word | Timekeeping software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mathematics | Production and Processing | Mechanical | English Language | Administration and Management | Design | Education and Training</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Manual Dexterity | Control Precision | Finger Dexterity | Trunk Strength | Extent Flexibility | Visualization | Multilimb Coordination | Speech Recognition | Static Strength | Selective Attention | Category Flexibility | Information Ordering | Deductive Reasoning | Problem Sensitivity | Inductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Time Pressure | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Spend Time Bending or Twisting Your Body | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Cabinetmakers and Bench Carpenters | Cement Masons and Concrete Finishers | Cutters and Trimmers, Hand | Etchers and Engravers | Furniture Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Jewelers and Precious Stone and Metal Workers | Layout Workers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Wood | Rock Splitters, Quarry | Stonemasons | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Tile and Stone Setters | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Cut or carve stone according to diagrams and patterns.</t>
+  </si>
+  <si>
+    <t>Carve designs or figures in full or bas relief on stone, employing knowledge of stone carving techniques and sense of artistry to produce carvings consistent with designers' plans. | Carve rough designs freehand or by chipping along marks on stone, using mallets and chisels or pneumatic tools. | Copy drawings on rough clay or plaster models. | Cut, shape, and finish rough blocks of building or monumental stone, according to diagrams or patterns. | Dress stone surfaces, using bushhammers. | Drill holes and cut or carve moldings and grooves in stone, according to diagrams and patterns. | Guide nozzles over stone, following stencil outlines, or chip along marks to create designs or to work surfaces down to specified finishes. | Lay out designs or dimensions from sketches or blueprints on stone surfaces, freehand or by transferring them from tracing paper, using scribes or chalk and measuring instruments. | Load sandblasting equipment with abrasives, attach nozzles to hoses, and turn valves to admit compressed air and activate jets. | Move fingers over surfaces of carvings to ensure smoothness of finish. | Remove or add stencils during blasting to create differing cut depths, intricate designs, or rough, pitted finishes. | Select chisels, pneumatic or surfacing tools, or sandblasting nozzles, and determine sequence of use. | Shape, trim, or touch up roughed-out designs with appropriate tools to finish carvings. | Smooth surfaces of carvings, using rubbing stones. | Study artistic objects or graphic materials, such as models, sketches, or blueprints, to plan carving or cutting techniques. | Verify depths and dimensions of cuts or carvings to ensure adherence to specifications, blueprints, or models, using measuring instruments.</t>
+  </si>
+  <si>
+    <t>51-9195.04</t>
+  </si>
+  <si>
+    <t>Glass Blowers, Molders, Benders, and Finishers</t>
+  </si>
+  <si>
+    <t>Gaffer | Glass Bender | Glass Blower | Glass Lathe Operator | Glass Tube Bender | Glassblower | Neon Glass Bender | Neon Tube Bender</t>
+  </si>
+  <si>
+    <t>Billing software | Inventory control software | Microsoft Excel | Microsoft Outlook</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Design | Mechanical | Customer and Personal Service | Engineering and Technology | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Control Precision | Reaction Time | Visual Color Discrimination | Visualization | Manual Dexterity | Finger Dexterity | Selective Attention | Rate Control | Multilimb Coordination | Perceptual Speed | Trunk Strength | Category Flexibility | Information Ordering | Problem Sensitivity | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Exposed to Minor Burns, Cuts, Bites, or Stings | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Spend Time Standing | Consequence of Error | Pace Determined by Speed of Equipment | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Metal-Refining Furnace Operators and Tenders | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Ophthalmic Laboratory Technicians | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool and Die Makers | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Shape molten glass according to patterns.</t>
+  </si>
+  <si>
+    <t>Blow tubing into specified shapes to prevent glass from collapsing, using compressed air or own breath, or blow and rotate gathers in molds or on boards to obtain final shapes. | Cut lengths of tubing to specified sizes, using files or cutting wheels. | Design and create glass objects, using blowpipes and artisans' hand tools and equipment. | Determine types and quantities of glass required to fabricate products. | Develop sketches of glass products into blueprint specifications, applying knowledge of glass technology and glass blowing. | Heat glass to pliable stage, using gas flames or ovens and rotating glass to heat it uniformly. | Inspect, weigh, and measure products to verify conformance to specifications, using instruments such as micrometers, calipers, magnifiers, or rulers. | Operate and maintain finishing machines to grind, drill, sand, bevel, decorate, wash, or polish glass or glass products. | Place glass into dies or molds of presses and control presses to form products, such as glassware components or optical blanks. | Place rubber hoses on ends of tubing and charge tubing with gas. | Record manufacturing information, such as quantities, sizes, or types of goods produced. | Repair broken scrolls by replacing them with new sections of tubing. | Set up and adjust machine press stroke lengths and pressures and regulate oven temperatures, according to glass types to be processed. | Shape, bend, or join sections of glass, using paddles, pressing and flattening hand tools, or cork. | Spray or swab molds with oil solutions to prevent adhesion of glass. | Superimpose bent tubing on asbestos patterns to ensure accuracy.</t>
+  </si>
+  <si>
+    <t>51-9195.05</t>
+  </si>
+  <si>
+    <t>Potters, Manufacturing</t>
+  </si>
+  <si>
+    <t>Clay Mixer | Glazer | Jigger Artisan | Jigger Machine Operator | Jiggerman | Kiln Worker | Potter | Pottery Manufacturer | Production Potter | Pugmill Operator</t>
+  </si>
+  <si>
+    <t>Inventory control software | Microsoft Excel | Microsoft Outlook</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Fine Arts | Production and Processing | Design | Customer and Personal Service | Chemistry | Administration and Management | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Control Precision | Near Vision | Visualization | Multilimb Coordination | Selective Attention | Category Flexibility | Information Ordering | Deductive Reasoning | Originality | Inductive Reasoning | Problem Sensitivity | Fluency of Ideas | Oral Expression | Oral Comprehension | Speech Recognition | Visual Color Discrimination | Rate Control</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Spend Time Making Repetitive Motions | Frequency of Decision Making | Importance of Repeating Same Tasks | Importance of Being Exact or Accurate | E-Mail | Indoors, Environmentally Controlled | Contact With Others | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Craft Artists | Etchers and Engravers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Foundry Mold and Coremakers | Furniture Finishers | Glass Blowers, Molders, Benders, and Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Jewelers and Precious Stone and Metal Workers | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Patternmakers, Wood | Pourers and Casters, Metal | Refractory Materials Repairers, Except Brickmasons | Sewers, Hand | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Operate production machines such as pug mill, jigger machine, or potter's wheel to process clay in manufacture of ceramic, pottery and stoneware products.</t>
+  </si>
+  <si>
+    <t>Adjust pressures, temperatures, and trimming tool settings as required. | Adjust wheel speeds according to the feel of the clay as pieces enlarge and walls become thinner. | Attach handles to pottery pieces. | Design clay forms and molds, and decorations for forms. | Design spaces to display pottery for sale. | Examine finished ware for defects and measure dimensions, using rule and thickness gauge. | Maintain supplies of tools, equipment, and materials, and order additional supplies as needed. | Mix and apply glazes to pottery pieces, using tools, such as spray guns. | Move pieces from wheels so that they can dry. | Operate drying chambers to dry or finish molded ceramic ware. | Operate gas or electric kilns to fire pottery pieces. | Operate pug mills to blend and extrude clay. | Pack and ship pottery to stores or galleries for retail sale. | Perform test-fires of pottery to determine how to achieve specific colors and textures. | Position balls of clay in centers of potters' wheels, and start motors or pump treadles with feet to revolve wheels. | Prepare work for sale or exhibition, and maintain relationships with retail, pottery, art, and resource networks that can facilitate sale or exhibition of work. | Press thumbs into centers of revolving clay to form hollows, and press on the inside and outside of emerging clay cylinders with hands and fingers, gradually raising and shaping clay to desired forms and sizes. | Pull wires through bases of articles and wheels to separate finished pieces. | Raise and shape clay into wares, such as vases and pitchers, on revolving wheels, using hands, fingers, and thumbs. | Smooth surfaces of finished pieces, using rubber scrapers and wet sponges. | Start machine units and conveyors and observe lights and gauges on panel board to verify operational efficiency. | Teach pottery classes. | Verify accuracy of shapes and sizes of objects, using calipers and templates.</t>
+  </si>
+  <si>
+    <t>51-9196.00</t>
+  </si>
+  <si>
+    <t>Paper Goods Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Corrugator Operator | Cup Room Technician | Folder Machine Operator | Gluer Operator | Paper Cutter Operator | Paper Machine Backtender | Paper Machine Operator | Stitching Machine Operator</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Microsoft Excel | Microsoft Office software | Microsoft Word | Objectif Lune PrintShop Mail | Quark enterprise publishing software | Virtual Systems Mail-Shop</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics | Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Problem Sensitivity | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Selective Attention | Information Ordering | Oral Expression | Oral Comprehension | Reaction Time | Rate Control | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Contact With Others | Frequency of Decision Making | Health and Safety of Other Workers | Time Pressure | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Pace Determined by Speed of Equipment | Exposed to Hazardous Equipment | Exposed to Contaminants | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Print Binding and Finishing Workers | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sewing Machine Operators | Textile Cutting Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend paper goods machines that perform a variety of functions, such as converting, sawing, corrugating, banding, wrapping, boxing, stitching, forming, or sealing paper or paperboard sheets into products.</t>
+  </si>
+  <si>
+    <t>Adjust guide assemblies, forming bars, and folding mechanisms according to specifications, using hand tools. | Cut products to specified dimensions, using hand or power cutters. | Disassemble machines to maintain, repair, or replace broken or worn parts, using hand or power tools. | Examine completed work to detect defects and verify conformance to work orders, and adjust machinery as necessary to correct production problems. | Fill glue and paraffin reservoirs, and position rollers to dispense glue onto paperboard. | Install attachments to machines for gluing, folding, printing, or cutting. | Lift tote boxes of finished cartons, and dump cartons into feed hoppers. | Measure, space, and set saw blades, cutters, and perforators, according to product specifications. | Monitor finished cartons as they drop from forming machines into rotating hoppers and into gravity feed chutes to prevent jamming. | Observe operation of various machines to detect and correct machine malfunctions such as improper forming, glue flow, or pasteboard tension. | Place rolls of paper or cardboard on machine feed tracks, and thread paper through gluing, coating, and slitting rollers. | Remove finished cores, and stack or place them on conveyors for transfer to other work areas. | Stamp products with information such as dates, using hand stamps or automatic stamping devices. | Start machines and move controls to regulate tension on pressure rolls, to synchronize speed of machine components, and to adjust temperatures of glue or paraffin.</t>
+  </si>
+  <si>
+    <t>51-9197.00</t>
+  </si>
+  <si>
+    <t>Tire Builders</t>
+  </si>
+  <si>
+    <t>Buffer | Recapper | Retread Associate | Retread Technician | Retreader | Tire Assembler | Tire Builder | Tire Retreader | Tire Technician | Tread Builder Operator</t>
+  </si>
+  <si>
+    <t>IBM Lotus Notes | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Programmable logic controller PLC software | SAP software | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Administration and Management | Mechanical</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Arm-Hand Steadiness | Control Precision | Multilimb Coordination | Trunk Strength | Rate Control | Finger Dexterity | Near Vision | Extent Flexibility | Static Strength | Reaction Time | Selective Attention | Problem Sensitivity | Oral Comprehension | Stamina | Speech Recognition | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Spend Time Bending or Twisting Your Body | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Equipment | Time Pressure | Exposed to Hazardous Conditions | Contact With Others | Importance of Repeating Same Tasks | Exposed to Minor Burns, Cuts, Bites, or Stings | Pace Determined by Speed of Equipment | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Importance of Being Exact or Accurate | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Engine and Other Machine Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Fiberglass Laminators and Fabricators | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Industrial Machinery Mechanics | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Rail Car Repairers | Shoe Machine Operators and Tenders | Structural Metal Fabricators and Fitters | Tire Repairers and Changers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Operate machines to build tires.</t>
+  </si>
+  <si>
+    <t>Align treads with guides, start drums to wind treads onto plies, and slice ends. | Brush or spray solvents onto plies to ensure adhesion, and repeat process as specified, alternating direction of each ply to strengthen tires. | Buff tires according to specifications for width and undertread depth. | Build semi-raw rubber treads onto buffed tire casings to prepare tires for vulcanization in recapping or retreading processes. | Clean and paint completed tires. | Cut plies at splice points, and press ends together to form continuous bands. | Depress pedals to collapse drums after processing is complete. | Depress pedals to rotate drums, and wind specified numbers of plies around drums to form tire bodies. | Fill cuts and holes in tires, using hot rubber. | Fit inner tubes and final layers of rubber onto tires. | Inspect worn tires for faults, cracks, cuts, and nail holes, and to determine if tires are suitable for retreading. | Measure tires to determine mold size requirements. | Place tires into molds for new tread. | Position ply stitcher rollers and drums according to width of stock, using hand tools and gauges. | Pull plies from supply racks, and align plies with edges of drums. | Roll hand rollers over rebuilt casings, exerting pressure to ensure adhesion between camelbacks and casings. | Rub cement sticks on drum edges to provide adhesive surfaces for plies. | Start rollers that bond tread and plies as drums revolve. | Trim excess rubber and imperfections during retreading processes. | Wind chafers and breakers onto plies.</t>
+  </si>
+  <si>
+    <t>51-9198.00</t>
+  </si>
+  <si>
+    <t>Helpers--Production Workers</t>
+  </si>
+  <si>
+    <t>Helper | Material Handler | Press Helper</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational databases | SAP software</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Static Strength | Trunk Strength | Manual Dexterity | Multilimb Coordination | Finger Dexterity | Arm-Hand Steadiness | Information Ordering | Problem Sensitivity | Extent Flexibility | Stamina | Perceptual Speed | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Pace Determined by Speed of Equipment | Contact With Others | Spend Time Standing | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Spend Time Bending or Twisting Your Body | Frequency of Decision Making | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Paper Goods Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Help production workers by performing duties requiring less skill. Duties include supplying or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Attach slings, ropes, or cables to objects such as pipes, hoses, or bundles. | Break up defective products for reprocessing. | Clean and lubricate equipment. | Count finished products to determine if product orders are complete. | Cut or break flashing from materials or products. | Examine products to verify conformance to quality standards. | Help production workers by performing duties of lesser skill, such as supplying or holding materials or tools, or cleaning work areas and equipment. | Lift raw materials, finished products, and packed items, manually or using hoists. | Load and unload items from machines, conveyors, and conveyances. | Mark or tag identification on parts. | Measure amounts of products, lengths of extruded articles, or weights of filled containers to ensure conformance to specifications. | Mix ingredients according to specified procedures or formulas. | Observe equipment operations so that malfunctions can be detected, and notify operators of any malfunctions. | Operate machinery used in the production process, or assist machine operators. | Pack and store materials and products. | Perform minor repairs to machines, such as replacing damaged or worn parts. | Place products in equipment or on work surfaces for further processing, inspecting, or wrapping. | Position spouts or chutes of storage bins so that containers can be filled. | Prepare raw materials for processing. | Read gauges or charts, and record data obtained. | Record information, such as the number of products tested, meter readings, or dates and times of product production. | Remove products, machine attachments, or waste material from machines. | Separate products according to weight, grade, size, or composition of materials used to produce them. | Signal coworkers to direct them to move products during the production process. | Start machines or equipment to begin production processes. | Tie products in bundles for further processing or shipment, following prescribed procedures. | Transfer finished products, raw materials, tools, or equipment between storage and work areas of plants and warehouses, by hand or using hand trucks or powered lift trucks. | Turn valves to regulate flow of liquids or air, to reverse machines, to start pumps, or to regulate equipment. | Unclamp and hoist full reels from braiding, winding, or other fabricating machines, using power hoists. | Wash work areas, machines, equipment, vehicles, or products.</t>
+  </si>
+  <si>
+    <t>51-9199.00</t>
+  </si>
+  <si>
+    <t>Production Workers, All Other</t>
+  </si>
+  <si>
+    <t>Factory Worker | Line Worker | Manufacturing Worker | Plant Worker | Process Worker | Production Associate | Production Operative | Production Worker | Shop Floor Worker | Manufacturing Operative</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | English Language | Mathematics | Public Safety and Security | Chemistry</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Helpers--Production Workers | Team Assemblers | Assemblers and Fabricators, All Other | Inspectors, Testers, Sorters, Samplers, and Weighers | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Machine Feeders and Offbearers | Cutters and Trimmers, Hand | Grinding and Polishing Workers, Hand | Mixing and Blending Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Adhesive Bonding Machine Operators and Tenders | Painting, Coating, and Decorating Workers | Computer Numerically Controlled Tool Operators | Machinists | Industrial Machinery Mechanics | First-Line Supervisors of Production and Operating Workers | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand</t>
+  </si>
+  <si>
+    <t>All production workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform production work in roles not classified separately. | Operate and tend production machinery according to work instructions. | Load raw materials and remove finished products from machines. | Inspect products for defects and remove items not meeting standards. | Measure, weigh, and count materials and finished goods. | Assemble, sort, label, and package products for shipment. | Record production quantities, downtime, and quality observations. | Clean and maintain machines, tools, and work areas. | Adjust machine settings within authorized limits to maintain quality. | Report equipment malfunctions and material shortages to supervisors. | Follow safety procedures, lockout rules, and protective equipment requirements. | Move materials between work stations using carts, hoists, and conveyors. | Participate in changeovers, setups, and line clearance activities. | Support continuous improvement and quality initiatives on the production floor.</t>
+  </si>
+  <si>
+    <t>53-1041.00</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors</t>
+  </si>
+  <si>
+    <t>Cargo Supervisor | Ground Operations Supervisor | Line Service Supervisor (LSS) | Loadmaster | Ramp Supervisor | Ramp and Cargo Supervisor</t>
+  </si>
+  <si>
+    <t>Cargo tracking system software | Corel WordPerfect Office Suite | Facebook | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Monitoring | Learning Strategies | Reading Comprehension | Writing | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | Transportation | English Language | Administration and Management | Administrative | Personnel and Human Resources | Mathematics | Education and Training | Computers and Electronics | Telecommunications | Production and Processing | Geography</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Far Vision | Deductive Reasoning | Near Vision | Multilimb Coordination | Selective Attention | Perceptual Speed | Speech Recognition | Information Ordering | Flexibility of Closure | Speech Clarity | Visualization | Time Sharing | Static Strength | Auditory Attention | Trunk Strength | Category Flexibility | Inductive Reasoning | Written Expression | Written Comprehension | Fluency of Ideas | Arm-Hand Steadiness | Speed of Closure | Reaction Time | Rate Control | Manual Dexterity | Depth Perception | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Time Pressure | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Work Outcomes and Results of Other Workers | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Environmentally Controlled | Conflict Situations | Coordinate or Lead Others in Accomplishing Work Activities | In an Open Vehicle or Operating Equipment | Importance of Repeating Same Tasks | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Consequence of Error | Written Letters and Memos | Exposed to Hazardous Equipment | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aircraft Service Attendants | Airfield Operations Specialists | Cargo and Freight Agents | Commercial Pilots | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | Freight Forwarders | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Railroad Conductors and Yardmasters | Tank Car, Truck, and Ship Loaders | Transportation Inspectors | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of ground crew in the loading, unloading, securing, and staging of aircraft cargo or baggage. May determine the quantity and orientation of cargo and compute aircraft center of gravity. May accompany aircraft as member of flight crew and monitor and handle cargo in flight, and assist and brief passengers on safety and emergency procedures. Includes loadmasters.</t>
+  </si>
+  <si>
+    <t>Accompany aircraft as a member of the flight crew to monitor and handle cargo in flight. | Calculate load weights for different aircraft compartments, using charts and computers. | Determine the quantity and orientation of cargo, and compute an aircraft's center of gravity. | Direct ground crews in the loading, unloading, securing, or staging of aircraft cargo or baggage. | Distribute cargo to maximize use of space. | Train new employees in areas such as safety procedures or equipment operation.</t>
+  </si>
+  <si>
+    <t>53-1042.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand</t>
+  </si>
+  <si>
+    <t>Floor Supervisor | Packaging Supervisor | Receiving Manager | Receiving Supervisor | Shipping Manager | Shipping Supervisor | Terminal Operations Manager | Warehouse Foreman | Warehouse Manager | Warehouse Supervisor</t>
+  </si>
+  <si>
+    <t>Corel WordPerfect Office Suite | Employee scheduling software | Inventory control software | Inventory management systems | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Database | SAP software | Sage ERP Accpac | Time and attendance software | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Critical Thinking | Reading Comprehension | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Production and Processing | Administration and Management | Mechanical | Computers and Electronics | English Language | Public Safety and Security | Mathematics | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Speech Recognition | Speech Clarity | Deductive Reasoning | Problem Sensitivity | Inductive Reasoning | Near Vision | Selective Attention | Information Ordering | Written Expression | Far Vision | Manual Dexterity | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Contact With Others | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Telephone Conversations | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Importance of Being Exact or Accurate | Time Pressure | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Written Letters and Memos | Level of Competition | Conflict Situations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Industrial Engineers | Industrial Production Managers | Production, Planning, and Expediting Clerks | Recycling Coordinators | Team Assemblers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate the activities of helpers, laborers, or material movers, hand.</t>
+  </si>
+  <si>
+    <t>Assess training needs of staff and arrange for or provide appropriate instruction. | Check specifications of materials loaded or unloaded against information contained in work orders. | Collaborate with workers and managers to solve work-related problems. | Conduct staff meetings to relay general information or to address specific topics, such as safety. | Counsel employees in work-related activities, personal growth, or career development. | Estimate material, time, and staffing requirements for a given project, based on work orders, job specifications, and experience. | Evaluate employee performance and prepare performance appraisals. | Examine freight to determine loading sequences. | Inform designated employees or departments of items loaded or problems encountered. | Inspect equipment for wear and for conformance to specifications. | Inspect job sites to determine the extent of maintenance or repairs needed. | Inventory supplies and requisition or purchase additional items, as necessary. | Maintain a safe working environment by monitoring safety procedures and equipment. | Participate in the hiring process by reviewing credentials, conducting interviews, or making hiring decisions or recommendations. | Perform the same work duties as those supervised, or perform more difficult or skilled tasks or assist in their performance. | Plan work schedules and assign duties to maintain adequate staff for effective performance of activities and response to fluctuating workloads. | Prepare and maintain work records and reports of information such as employee time and wages, daily receipts, or inspection results. | Provide assistance in balancing books, tracking, monitoring, or projecting a unit's budget needs, and in developing unit policies and procedures. | Quote prices to customers. | Recommend or initiate personnel actions, such as promotions, transfers, or disciplinary measures. | Resolve personnel problems, complaints, or formal grievances when possible, or refer them to higher-level supervisors for resolution. | Review work throughout the work process and at completion to ensure that it has been performed properly. | Schedule times of shipment and modes of transportation for materials. | Transmit and explain work orders to laborers.</t>
+  </si>
+  <si>
+    <t>53-1042.01</t>
+  </si>
+  <si>
+    <t>Recycling Coordinators</t>
+  </si>
+  <si>
+    <t>Heavy Equipment Supervisor | Recycle Coordinator | Recycling Coordinator | Recycling Manager | Recycling Program Manager | Recycling Specialist | Route Supervisor | Solid Waste Division Supervisor | Waste Reduction Coordinator</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational databases | SAP software | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Monitoring | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Administrative | Education and Training | Production and Processing | Mathematics | English Language | Public Safety and Security | Personnel and Human Resources | Computers and Electronics | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Deductive Reasoning | Information Ordering | Inductive Reasoning | Problem Sensitivity | Written Comprehension | Near Vision | Category Flexibility | Selective Attention | Written Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Determine Tasks, Priorities and Goals | Contact With Others | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Indoors, Not Environmentally Controlled | Time Pressure | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Facilities Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Production and Operating Workers | General and Operations Managers | Hazardous Materials Removal Workers | Industrial Production Managers | Logisticians | Management Analysts | Production, Planning, and Expediting Clerks | Project Management Specialists | Recycling and Reclamation Workers | Refuse and Recyclable Material Collectors | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Supervise curbside and drop-off recycling programs for municipal governments or private firms.</t>
+  </si>
+  <si>
+    <t>Assign truck drivers or recycling technicians to routes. | Coordinate recycling collection schedules to optimize service and efficiency. | Coordinate shipments of recycling materials with shipping brokers or processing companies. | Create or manage recycling operations budgets. | Design community solid and hazardous waste management programs. | Develop community or corporate recycling plans and goals to minimize waste and conform to resource constraints. | Identify or investigate new opportunities for materials to be collected and recycled. | Implement grant-funded projects, monitoring and reporting progress in accordance with sponsoring agency requirements. | Inspect physical condition of recycling or hazardous waste facility for compliance with safety, quality, and service standards. | Investigate violations of solid waste or recycling ordinances. | Maintain logs of recycling materials received or shipped to processing companies. | Make presentations to educate the public on how to recycle or on the environmental advantages of recycling. | Negotiate contracts with waste management or other firms. | Operate fork lifts, skid loaders, or trucks to move or store recyclable materials. | Operate recycling processing equipment, such as sorters, balers, crushers, and granulators to sort and process materials. | Oversee campaigns to promote recycling or waste reduction programs in communities or private companies. | Oversee recycling pick-up or drop-off programs to ensure compliance with community ordinances. | Prepare bills of lading, statements of shipping records, or customer receipts related to recycling or hazardous material services. | Prepare grant applications to fund recycling programs or program enhancements. | Provide training to recycling technicians or community service workers on topics such as safety, solid waste processing, or general recycling operations. | Review customer requests for service to determine service needs and deploy appropriate resources to provide service. | Schedule movement of recycling materials into and out of storage areas. | Supervise recycling technicians, community service workers, or other recycling operations employees or volunteers.</t>
+  </si>
+  <si>
+    <t>53-1043.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Material-Moving Machine and Vehicle Operators</t>
+  </si>
+  <si>
+    <t>Cargo Manager | DC Supervisor (Distribution Center Supervisor) | Dock Supervisor | Driver Manager | Fleet Manager | Shipping Manager | Street Supervisor | Trainmaster | Transportation Supervisor | Warehouse Supervisor</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension | Monitoring | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Administration and Management | Customer and Personal Service | Mathematics | English Language | Production and Processing | Personnel and Human Resources | Public Safety and Security | Computers and Electronics | Transportation | Administrative | Psychology | Education and Training | Law and Government | Economics and Accounting</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Written Expression | Near Vision | Speech Clarity | Speech Recognition | Information Ordering | Far Vision | Selective Attention | Flexibility of Closure | Category Flexibility | Number Facility | Originality | Fluency of Ideas | Time Sharing</t>
+  </si>
+  <si>
+    <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Level of Competition | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Conflict Situations | Time Pressure | Written Letters and Memos | Consequence of Error | Outdoors, Exposed to All Weather Conditions | Dealing With Unpleasant, Angry, or Discourteous People | Indoors, Not Environmentally Controlled | Spend Time Walking or Running | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Importance of Repeating Same Tasks | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Industrial Production Managers | Railroad Conductors and Yardmasters | Recycling Coordinators | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of material-moving machine and vehicle operators and helpers.</t>
+  </si>
+  <si>
+    <t>Assist workers in tasks, such as loading vehicles. | Compute or estimate cash, payroll, transportation, personnel, or storage requirements. | Confer with customers, supervisors, contractors, or other personnel to exchange information or to resolve problems. | Direct workers in transportation or related services, such as pumping, moving, storing, or loading or unloading of materials. | Dispatch personnel and vehicles in response to telephone or radio reports of emergencies. | Drive vehicles or operate machines or equipment to complete work assignments or to assist workers. | Enforce safety rules and regulations. | Examine, measure, or weigh cargo or materials to determine specific handling requirements. | Explain and demonstrate work tasks to new workers or assign training tasks to experienced workers. | Inspect or test materials, stock, vehicles, equipment, or facilities to ensure that they are safe, free of defects, and consistent with specifications. | Interpret transportation or tariff regulations, shipping orders, safety regulations, or company policies and procedures for workers. | Maintain or verify records of time, materials, expenditures, or crew activities. | Monitor field work to ensure proper performance and use of materials. | Perform or schedule repairs or preventive maintenance of vehicles or other equipment. | Plan and establish schedules. | Plan work assignments and equipment allocations to meet transportation, operations or production goals. | Prepare, compile, and submit reports on work activities, operations, production, or work-related accidents. | Recommend and implement measures to improve worker motivation, equipment performance, work methods, or customer services. | Recommend or implement personnel actions, such as employee selection, evaluation, rewards, or disciplinary actions. | Requisition needed personnel, supplies, equipment, parts, or repair services. | Resolve worker problems or collaborate with employees to assist in problem resolution. | Review orders, production schedules, blueprints, or shipping or receiving notices to determine work sequences and material shipping dates, types, volumes, or destinations.</t>
+  </si>
+  <si>
+    <t>53-1044.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Passenger Attendants</t>
+  </si>
+  <si>
+    <t>On Car Supervisor | Transportation Supervisor</t>
+  </si>
+  <si>
+    <t>Accellos Real Dispatch | Commercial vehicle operations CVO software | General ledger software | Inventory management systems | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | Scheduling software | Timekeeping software | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Transportation | Customer and Personal Service | Administration and Management | Public Safety and Security | English Language | Personnel and Human Resources | Education and Training | Geography</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Written Expression | Originality</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition | E-Mail | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Human Resources Specialists | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate activities of passenger attendants.</t>
+  </si>
+  <si>
+    <t>Analyze and record personnel or operational data and write related activity reports. | Apply customer feedback to service improvement efforts. | Compute or estimate cash, payroll, transportation, or personnel requirements. | Confer with customers, supervisors, contractors, or other personnel to exchange information or to resolve problems. | Direct or coordinate the activities of workers, such as flight or car attendants. | Enforce safety rules and regulations. | Explain and demonstrate work tasks to new workers or assign training tasks to experienced workers. | Inform workers about interests or special needs of specific groups. | Inspect materials, stock, vehicles, equipment, or facilities to ensure that they are safe, free of defects, and consistent with specifications. | Inspect work areas or operating equipment to ensure conformance to established standards in areas such as cleanliness or maintenance. | Meet with managers or other supervisors to stay informed of changes affecting operations. | Observe and evaluate workers' appearance and performance to ensure quality service and compliance with specifications. | Participate in continuing education to stay abreast of industry trends and developments. | Recommend and implement measures to improve worker motivation, work methods, or customer services. | Recruit and hire staff members. | Requisition necessary supplies, equipment, or services. | Resolve customer complaints regarding worker performance or services rendered. | Take disciplinary action to address performance problems. | Train workers in proper operational procedures and functions and explain company policies.</t>
+  </si>
+  <si>
+    <t>53-1049.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Transportation Workers, All Other</t>
+  </si>
+  <si>
+    <t>Dispatch Supervisor | Fleet Supervisor | Operations Supervisor | Terminal Supervisor | Transportation Supervisor | Transport Operations Supervisor | Yard Supervisor | Traffic Supervisor | Shift Transportation Supervisor | Depot Supervisor</t>
+  </si>
+  <si>
+    <t>Fleet management software | Transportation management software | Warehouse management system WMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Database software | Scheduling software | Web browser software | Microsoft Outlook | Enterprise resource planning ERP system | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Transportation | Administration and Management | Public Safety and Security | Customer and Personal Service | English Language | Personnel and Human Resources | Education and Training | Law and Government | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition | Consequence of Error | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | Aircraft Cargo Handling Supervisors | Recycling Coordinators | Transportation, Storage, and Distribution Managers | Logisticians | Logistics Analysts | Supply Chain Managers | Dispatchers, Except Police, Fire, and Ambulance | Cargo and Freight Agents | Freight Forwarders | Transportation Inspectors | Airfield Operations Specialists | Heavy and Tractor-Trailer Truck Drivers | Bus Drivers, Transit and Intercity | Railroad Conductors and Yardmasters | General and Operations Managers | Production, Planning, and Expediting Clerks | Occupational Health and Safety Specialists</t>
+  </si>
+  <si>
+    <t>All first-line supervisors of transportation workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Supervise transportation workers in roles not classified separately. | Assign routes, vehicles, equipment, and duty schedules to personnel. | Monitor operations to ensure on-time performance and service standards. | Enforce safety regulations, hours-of-service rules, and company policies. | Investigate accidents, incidents, delays, and customer complaints. | Train and evaluate drivers, operators, and support personnel. | Inspect vehicles and equipment for serviceability and regulatory compliance. | Coordinate maintenance, fueling, and repair scheduling with service staff. | Maintain records of trips, hours, inspections, and personnel actions. | Prepare operating reports and analyze performance metrics. | Resolve operational problems such as breakdowns, reroutes, and staffing gaps. | Communicate with customers, dispatchers, and other departments. | Recommend improvements to routes, schedules, and procedures. | Manage supplies, equipment, and budgets for the assigned unit.</t>
+  </si>
+  <si>
+    <t>53-2011.00</t>
+  </si>
+  <si>
+    <t>Airline Pilots, Copilots, and Flight Engineers</t>
+  </si>
+  <si>
+    <t>Airbus Captain | Airline Captain | Airline Pilot | Captain | Check Airman | Co-Pilot | Commercial Airline Pilot | First Officer (FO) | Line Pilot | Pilot</t>
+  </si>
+  <si>
+    <t>AeroPlanner | AirSmith FlightPrompt | Airline Pilots Daily Aviation Log PPC | CoPilot Flight Planning &amp; E6B | Document Object Model DOM Scripting | Electronic aircraft information databases | IFT-Pro | MJICCS PilotLog | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | Pilot Navigator Software Load Balance | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | R | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | doXstor Flight Level Logbook</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Reading Comprehension | Speaking | Active Learning | Mathematics | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Transportation | English Language | Public Safety and Security | Geography | Mechanical | Mathematics | Computers and Electronics | Physics | Law and Government | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Response Orientation | Problem Sensitivity | Control Precision | Far Vision | Near Vision | Reaction Time | Rate Control | Depth Perception | Deductive Reasoning | Perceptual Speed | Flexibility of Closure | Spatial Orientation | Selective Attention | Time Sharing | Arm-Hand Steadiness | Multilimb Coordination | Oral Comprehension | Written Comprehension | Oral Expression | Inductive Reasoning | Information Ordering | Peripheral Vision | Speech Clarity | Hearing Sensitivity | Speech Recognition | Visual Color Discrimination | Glare Sensitivity | Manual Dexterity | Visualization | Speed of Closure | Night Vision | Number Facility | Auditory Attention | Finger Dexterity | Memorization | Mathematical Reasoning | Written Expression | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Work With or Contribute to a Work Group or Team | Time Pressure | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Freedom to Make Decisions | Frequency of Decision Making | Level of Competition | Physical Proximity | E-Mail | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Public Speaking | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Extremely Bright or Inadequate Lighting Conditions | Determine Tasks, Priorities and Goals | Exposed to High Places | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Very Hot or Cold Temperatures | Degree of Automation | Exposed to Radiation | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Aircraft Mechanics and Service Technicians | Aircraft Service Attendants | Airfield Operations Specialists | Aviation Inspectors | Avionics Technicians | Captains, Mates, and Pilots of Water Vessels | Commercial Pilots | First-Line Supervisors of Passenger Attendants | Flight Attendants | Locomotive Engineers | Motorboat Operators | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Sailors and Marine Oilers | Ship Engineers | Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Pilot and navigate the flight of fixed-wing aircraft, usually on scheduled air carrier routes, for the transport of passengers and cargo. Requires Federal Air Transport certificate and rating for specific aircraft type used. Includes regional, national, and international airline pilots and flight instructors of airline pilots.</t>
+  </si>
+  <si>
+    <t>Brief crews about flight details, such as destinations, duties, and responsibilities. | Check passenger and cargo distributions and fuel amounts to ensure that weight and balance specifications are met. | Choose routes, altitudes, and speeds that will provide the fastest, safest, and smoothest flights. | Conduct in-flight tests and evaluations at specified altitudes and in all types of weather to determine the receptivity and other characteristics of equipment and systems. | Confer with flight dispatchers and weather forecasters to keep abreast of flight conditions. | Contact control towers for takeoff clearances, arrival instructions, and other information, using radio equipment. | Coordinate flight activities with ground crews and air traffic control and inform crew members of flight and test procedures. | Direct activities of aircraft crews during flights. | Evaluate other pilots or pilot-license applicants for proficiency. | File instrument flight plans with air traffic control to ensure that flights are coordinated with other air traffic. | Inspect aircraft for defects and malfunctions, according to pre-flight checklists. | Instruct other pilots and student pilots in aircraft operations and the principles of flight. | Make announcements regarding flights, using public address systems. | Monitor engine operation, fuel consumption, and functioning of aircraft systems during flights. | Monitor gauges, warning devices, and control panels to verify aircraft performance and to regulate engine speed. | Order changes in fuel supplies, loads, routes, or schedules to ensure safety of flights. | Perform minor maintenance work, or arrange for major maintenance. | Plan and formulate flight activities and test schedules and prepare flight evaluation reports. | Record in log books information, such as flight times, distances flown, and fuel consumption. | Respond to and report in-flight emergencies and malfunctions. | Start engines, operate controls, and pilot airplanes to transport passengers, mail, or freight, adhering to flight plans, regulations, and procedures. | Steer aircraft along planned routes, using autopilot and flight management computers. | Use instrumentation to guide flights when visibility is poor. | Work as part of a flight team with other crew members, especially during takeoffs and landings.</t>
+  </si>
+  <si>
+    <t>53-2012.00</t>
+  </si>
+  <si>
+    <t>Commercial Pilots</t>
+  </si>
+  <si>
+    <t>Captain | Charter Pilot | Check Airman | Commercial Helicopter Pilot | Commercial Pilot | EMS Helicopter Pilot (Emergency Medical Service Helicopter Pilot) | First Officer | Helicopter Pilot | Line Pilot | Pilot</t>
+  </si>
+  <si>
+    <t>Adobe Creative Cloud software | AeroPlanner | Aeronautical charts | AirSmith FlightPrompt | Airdata | Airline Pilots Daily Aviation Log PPC | ArduPilot Mission Planner | Calibration software | CloudCompare | ESRI Site Scan for ArcGIS | Electronic aircraft information databases | FLIR Thermal Studio Suite | Flight simulation software | Kitty Hawk | LP360 | Litchi | MJICCS PilotLog | Microsoft Office software | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | OpenDroneMap | Pilot Navigator Software Load Balance | Pix4D Pix4Dcapture | Pix4D Pix4Dmapper | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | Standard generalized markup language SGML | UgCS | doXstor Flight Level Logbook</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Speaking | Reading Comprehension | Active Learning | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Transportation | Geography | Public Safety and Security | Mechanical | Law and Government | Computers and Electronics | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Perceptual Speed | Control Precision | Near Vision | Response Orientation | Reaction Time | Far Vision | Depth Perception | Selective Attention | Oral Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Multilimb Coordination | Rate Control | Spatial Orientation | Written Comprehension | Speech Recognition | Speech Clarity | Time Sharing | Flexibility of Closure | Manual Dexterity | Written Expression | Arm-Hand Steadiness | Visualization | Auditory Attention | Hearing Sensitivity | Glare Sensitivity | Speed of Closure | Category Flexibility | Originality | Fluency of Ideas | Peripheral Vision | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>E-Mail | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Frequency of Decision Making | Spend Time Sitting | Telephone Conversations | Physical Proximity | In an Enclosed Vehicle or Operate Enclosed Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Time Pressure | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Repeating Same Tasks | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Aircraft Mechanics and Service Technicians | Aircraft Service Attendants | Airfield Operations Specialists | Airline Pilots, Copilots, and Flight Engineers | Aviation Inspectors | Avionics Technicians | Camera Operators, Television, Video, and Film | Captains, Mates, and Pilots of Water Vessels | Dispatchers, Except Police, Fire, and Ambulance | Flight Attendants | Heavy and Tractor-Trailer Truck Drivers | Locomotive Engineers | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Conductors and Yardmasters | Remote Sensing Technicians | Ship Engineers | Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Pilot and navigate the flight of fixed-wing aircraft on nonscheduled air carrier routes, or helicopters. Requires Commercial Pilot certificate. Includes charter pilots with similar certification, and air ambulance and air tour pilots. Excludes regional, national, and international airline pilots.</t>
+  </si>
+  <si>
+    <t>Check aircraft prior to flights to ensure that the engines, controls, instruments, and other systems are functioning properly. | Check baggage or cargo to ensure that it has been loaded correctly. | Choose routes, altitudes, and speeds that will provide the fastest, safest, and smoothest flights. | Co-pilot aircraft or perform captain's duties, as required. | Conduct in-flight tests and evaluations at specified altitudes and in all types of weather to determine the receptivity and other characteristics of equipment and systems. | Consider airport altitudes, outside temperatures, plane weights, and wind speeds and directions to calculate the speed needed to become airborne. | Contact control towers for takeoff clearances, arrival instructions, and other information, using radio equipment. | Coordinate flight activities with ground crews and air traffic control, and inform crew members of flight and test procedures. | File instrument flight plans with air traffic control so that flights can be coordinated with other air traffic. | Fly with other pilots or pilot-license applicants to evaluate their proficiency. | Instruct other pilots and student pilots in aircraft operations. | Monitor engine operation, fuel consumption, and functioning of aircraft systems during flights. | Obtain and review data such as load weights, fuel supplies, weather conditions, and flight schedules to determine flight plans and identify needed changes. | Order changes in fuel supplies, loads, routes, or schedules to ensure safety of flights. | Perform minor aircraft maintenance and repair work, or arrange for major maintenance. | Plan and formulate flight activities and test schedules and prepare flight evaluation reports. | Plan flights according to government and company regulations, using aeronautical charts and navigation instruments. | Request changes in altitudes or routes as circumstances dictate. | Rescue and evacuate injured persons. | Start engines, operate controls, and pilot airplanes to transport passengers, mail, or freight according to flight plans, regulations, and procedures. | Supervise other crew members. | Teach company regulations and procedures to other pilots. | Use instrumentation to pilot aircraft when visibility is poor. | Write specified information in flight records, such as flight times, altitudes flown, and fuel consumption.</t>
+  </si>
+  <si>
+    <t>53-2021.00</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers</t>
+  </si>
+  <si>
+    <t>Air Traffic Control Specialist (ATCS) | Air Traffic Controller (ATC) | Center Air Traffic Controller (Center ATC) | Certified Professional Controller (CPC) | Control Tower Operator | Enroute Air Traffic Controller (Enroute ATC) | Radar Air Traffic Controller | Terminal Air Traffic Control Specialist (Terminal ATC Specialist) | Tower Air Traffic Controller (Tower ATC)</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Advanced technologies and oceanic procedures ATOP | Automated radar terminal systems ARTS | Center TRACON automation systems CTAS | Direct-to-tool software | En route descent advisor EDA | Expedite departure path EDP software | Final approach spacing tool FAST | Flight simulation software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Multi-center traffic management advisor McTMA | Really Simple Syndication RSS | SAP software | Traffic management advisor TMA software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Active Learning | Reading Comprehension | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Transportation | English Language | Public Safety and Security | Education and Training | Customer and Personal Service | Geography | Telecommunications | Mathematics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Expression | Oral Comprehension | Selective Attention | Deductive Reasoning | Flexibility of Closure | Speed of Closure | Inductive Reasoning | Perceptual Speed | Time Sharing | Near Vision | Far Vision | Speech Clarity | Information Ordering | Speech Recognition | Written Comprehension | Category Flexibility | Auditory Attention | Visualization | Originality | Fluency of Ideas | Written Expression | Mathematical Reasoning | Visual Color Discrimination | Memorization | Number Facility</t>
+  </si>
+  <si>
+    <t>Frequency of Decision Making | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Contact With Others | Importance of Repeating Same Tasks | Spend Time Sitting | Conflict Situations | Freedom to Make Decisions | Physical Proximity | Deal With External Customers or the Public in General | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Telephone Conversations | Degree of Automation | Spend Time Making Repetitive Motions | Work Outcomes and Results of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Aircraft Service Attendants | Airfield Operations Specialists | Airline Pilots, Copilots, and Flight Engineers | Aviation Inspectors | Avionics Technicians | Bus Drivers, Transit and Intercity | Commercial Pilots | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Passenger Attendants | Flight Attendants | Locomotive Engineers | Power Distributors and Dispatchers | Public Safety Telecommunicators | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Subway and Streetcar Operators | Traffic Technicians | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Control air traffic on and within vicinity of airport, and movement of air traffic between altitude sectors and control centers, according to established procedures and policies. Authorize, regulate, and control commercial airline flights according to government or company regulations to expedite and ensure flight safety.</t>
+  </si>
+  <si>
+    <t>Alert airport emergency services in cases of emergency or when aircraft are experiencing difficulties. | Analyze factors such as weather reports, fuel requirements, or maps to determine air routes. | Check conditions and traffic at different altitudes in response to pilots' requests for altitude changes. | Compile information about flights from flight plans, pilot reports, radar, or observations. | Complete daily activity reports and keep records of messages from aircraft. | Conduct pre-flight briefings on weather conditions, suggested routes, altitudes, indications of turbulence, or other flight safety information. | Contact pilots by radio to provide meteorological, navigational, or other information. | Determine the timing or procedures for flight vector changes. | Direct ground traffic, including taxiing aircraft, maintenance or baggage vehicles, or airport workers. | Direct pilots to runways when space is available or direct them to maintain a traffic pattern until there is space for them to land. | Inform pilots about nearby planes or potentially hazardous conditions, such as weather, speed and direction of wind, or visibility problems. | Initiate or coordinate searches for missing aircraft. | Inspect, adjust, or control radio equipment or airport lights. | Issue landing and take-off authorizations or instructions. | Maintain radio or telephone contact with adjacent control towers, terminal control units, or other area control centers to coordinate aircraft movement. | Monitor aircraft within a specific airspace, using radar, computer equipment, or visual references. | Monitor or direct the movement of aircraft within an assigned air space or on the ground at airports to minimize delays and maximize safety. | Organize flight plans or traffic management plans to prepare for planes about to enter assigned airspace. | Provide flight path changes or directions to emergency landing fields for pilots traveling in bad weather or in emergency situations. | Provide on-the-job training to new air traffic controllers. | Relay air traffic information, such as courses, altitudes, or expected arrival times, to control centers. | Review records or reports for clarity and completeness and maintain records or reports, as required under federal law. | Transfer control of departing flights to traffic control centers and accept control of arriving flights.</t>
+  </si>
+  <si>
+    <t>Road GeoManager | Accellos Real Dispatch | Actsoft Comet Tracker | Barcode software | Bill of lading software | CAPE Systems CAPE PACK | CAPE Systems TRUCKFILL | Commercial vehicle operations CVO software | Coptimal Logics AutoLoad Pro | Creative Systems Corporation Freight-Link System | Fleet management systems | General ledger software | JDA Manugistics | Load optimization software | MagicLogic Optimization Cube-IQ | Mapping software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Optimum Logistics LoadPlanner | Proof of delivery POD software | SAP software | Scheduling software | Softtruck CargoWiz | Starre Enterprises Star Bill of Lading | Strategic Business Systems Proof of Delivery | TOPS Engineering MaxLoad Pro | UPS Logistics Technologies Roadnet Transportation Suite | Warehouse management system WMS | Web browser software | XATA XATANET</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1955,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" t="s">
+        <v>171</v>
+      </c>
+      <c r="J16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" t="s">
+        <v>181</v>
+      </c>
+      <c r="I17" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18" t="s">
+        <v>191</v>
+      </c>
+      <c r="H18" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" t="s">
+        <v>200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>201</v>
+      </c>
+      <c r="G19" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" t="s">
+        <v>203</v>
+      </c>
+      <c r="I19" t="s">
+        <v>204</v>
+      </c>
+      <c r="J19" t="s">
+        <v>205</v>
+      </c>
+      <c r="K19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" t="s">
+        <v>216</v>
+      </c>
+      <c r="K20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F21" t="s">
+        <v>223</v>
+      </c>
+      <c r="G21" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" t="s">
+        <v>225</v>
+      </c>
+      <c r="I21" t="s">
+        <v>226</v>
+      </c>
+      <c r="J21" t="s">
+        <v>227</v>
+      </c>
+      <c r="K21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22" t="s">
+        <v>235</v>
+      </c>
+      <c r="H22" t="s">
+        <v>236</v>
+      </c>
+      <c r="I22" t="s">
+        <v>237</v>
+      </c>
+      <c r="J22" t="s">
+        <v>238</v>
+      </c>
+      <c r="K22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" t="s">
+        <v>241</v>
+      </c>
+      <c r="C23" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" t="s">
+        <v>244</v>
+      </c>
+      <c r="F23" t="s">
+        <v>245</v>
+      </c>
+      <c r="G23" t="s">
+        <v>246</v>
+      </c>
+      <c r="H23" t="s">
+        <v>247</v>
+      </c>
+      <c r="I23" t="s">
+        <v>248</v>
+      </c>
+      <c r="J23" t="s">
+        <v>249</v>
+      </c>
+      <c r="K23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" t="s">
+        <v>255</v>
+      </c>
+      <c r="H24" t="s">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
+        <v>257</v>
+      </c>
+      <c r="J24" t="s">
+        <v>258</v>
+      </c>
+      <c r="K24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" t="s">
+        <v>264</v>
+      </c>
+      <c r="F25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" t="s">
+        <v>267</v>
+      </c>
+      <c r="I25" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" t="s">
+        <v>269</v>
+      </c>
+      <c r="K25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" t="s">
+        <v>279</v>
+      </c>
+      <c r="J26" t="s">
+        <v>280</v>
+      </c>
+      <c r="K26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" t="s">
+        <v>286</v>
+      </c>
+      <c r="F27" t="s">
+        <v>287</v>
+      </c>
+      <c r="G27" t="s">
+        <v>288</v>
+      </c>
+      <c r="H27" t="s">
+        <v>289</v>
+      </c>
+      <c r="I27" t="s">
+        <v>290</v>
+      </c>
+      <c r="J27" t="s">
+        <v>291</v>
+      </c>
+      <c r="K27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C28" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" t="s">
+        <v>296</v>
+      </c>
+      <c r="E28" t="s">
+        <v>297</v>
+      </c>
+      <c r="F28" t="s">
+        <v>298</v>
+      </c>
+      <c r="G28" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" t="s">
+        <v>300</v>
+      </c>
+      <c r="I28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J28" t="s">
+        <v>302</v>
+      </c>
+      <c r="K28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" t="s">
+        <v>307</v>
+      </c>
+      <c r="E29" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G29" t="s">
+        <v>310</v>
+      </c>
+      <c r="H29" t="s">
+        <v>311</v>
+      </c>
+      <c r="I29" t="s">
+        <v>312</v>
+      </c>
+      <c r="J29" t="s">
+        <v>313</v>
+      </c>
+      <c r="K29" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>315</v>
+      </c>
+      <c r="B30" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" t="s">
+        <v>319</v>
+      </c>
+      <c r="F30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" t="s">
+        <v>320</v>
+      </c>
+      <c r="H30" t="s">
+        <v>321</v>
+      </c>
+      <c r="I30" t="s">
+        <v>322</v>
+      </c>
+      <c r="J30" t="s">
+        <v>323</v>
+      </c>
+      <c r="K30" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>325</v>
+      </c>
+      <c r="B31" t="s">
+        <v>326</v>
+      </c>
+      <c r="C31" t="s">
+        <v>327</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" t="s">
+        <v>329</v>
+      </c>
+      <c r="H31" t="s">
+        <v>330</v>
+      </c>
+      <c r="I31" t="s">
+        <v>331</v>
+      </c>
+      <c r="J31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K31" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
+        <v>335</v>
+      </c>
+      <c r="C32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" t="s">
+        <v>338</v>
+      </c>
+      <c r="F32" t="s">
+        <v>339</v>
+      </c>
+      <c r="G32" t="s">
+        <v>340</v>
+      </c>
+      <c r="H32" t="s">
+        <v>341</v>
+      </c>
+      <c r="I32" t="s">
+        <v>342</v>
+      </c>
+      <c r="J32" t="s">
+        <v>343</v>
+      </c>
+      <c r="K32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>345</v>
+      </c>
+      <c r="B33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D33" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" t="s">
+        <v>351</v>
+      </c>
+      <c r="H33" t="s">
+        <v>352</v>
+      </c>
+      <c r="I33" t="s">
+        <v>353</v>
+      </c>
+      <c r="J33" t="s">
+        <v>354</v>
+      </c>
+      <c r="K33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B34" t="s">
+        <v>357</v>
+      </c>
+      <c r="C34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D34" t="s">
+        <v>359</v>
+      </c>
+      <c r="E34" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G34" t="s">
+        <v>361</v>
+      </c>
+      <c r="H34" t="s">
+        <v>362</v>
+      </c>
+      <c r="I34" t="s">
+        <v>363</v>
+      </c>
+      <c r="J34" t="s">
+        <v>364</v>
+      </c>
+      <c r="K34" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>366</v>
+      </c>
+      <c r="B35" t="s">
+        <v>367</v>
+      </c>
+      <c r="C35" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" t="s">
+        <v>369</v>
+      </c>
+      <c r="E35" t="s">
+        <v>370</v>
+      </c>
+      <c r="F35" t="s">
+        <v>371</v>
+      </c>
+      <c r="G35" t="s">
+        <v>372</v>
+      </c>
+      <c r="H35" t="s">
+        <v>373</v>
+      </c>
+      <c r="I35" t="s">
+        <v>374</v>
+      </c>
+      <c r="J35" t="s">
+        <v>375</v>
+      </c>
+      <c r="K35" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>377</v>
+      </c>
+      <c r="B36" t="s">
+        <v>378</v>
+      </c>
+      <c r="C36" t="s">
+        <v>379</v>
+      </c>
+      <c r="D36" t="s">
+        <v>380</v>
+      </c>
+      <c r="E36" t="s">
+        <v>381</v>
+      </c>
+      <c r="F36" t="s">
+        <v>382</v>
+      </c>
+      <c r="G36" t="s">
+        <v>383</v>
+      </c>
+      <c r="H36" t="s">
+        <v>384</v>
+      </c>
+      <c r="I36" t="s">
+        <v>385</v>
+      </c>
+      <c r="J36" t="s">
+        <v>386</v>
+      </c>
+      <c r="K36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>388</v>
+      </c>
+      <c r="B37" t="s">
+        <v>389</v>
+      </c>
+      <c r="C37" t="s">
+        <v>390</v>
+      </c>
+      <c r="D37" t="s">
+        <v>391</v>
+      </c>
+      <c r="E37" t="s">
+        <v>392</v>
+      </c>
+      <c r="F37" t="s">
+        <v>393</v>
+      </c>
+      <c r="G37" t="s">
+        <v>394</v>
+      </c>
+      <c r="H37" t="s">
+        <v>395</v>
+      </c>
+      <c r="I37" t="s">
+        <v>396</v>
+      </c>
+      <c r="J37" t="s">
+        <v>397</v>
+      </c>
+      <c r="K37" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>399</v>
+      </c>
+      <c r="B38" t="s">
+        <v>400</v>
+      </c>
+      <c r="C38" t="s">
+        <v>401</v>
+      </c>
+      <c r="D38" t="s">
+        <v>402</v>
+      </c>
+      <c r="E38" t="s">
+        <v>403</v>
+      </c>
+      <c r="F38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G38" t="s">
+        <v>405</v>
+      </c>
+      <c r="H38" t="s">
+        <v>406</v>
+      </c>
+      <c r="I38" t="s">
+        <v>407</v>
+      </c>
+      <c r="J38" t="s">
+        <v>408</v>
+      </c>
+      <c r="K38" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>410</v>
+      </c>
+      <c r="B39" t="s">
+        <v>411</v>
+      </c>
+      <c r="C39" t="s">
+        <v>412</v>
+      </c>
+      <c r="D39" t="s">
+        <v>413</v>
+      </c>
+      <c r="E39" t="s">
+        <v>414</v>
+      </c>
+      <c r="F39" t="s">
+        <v>415</v>
+      </c>
+      <c r="G39" t="s">
+        <v>416</v>
+      </c>
+      <c r="H39" t="s">
+        <v>417</v>
+      </c>
+      <c r="I39" t="s">
+        <v>418</v>
+      </c>
+      <c r="J39" t="s">
+        <v>419</v>
+      </c>
+      <c r="K39" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>421</v>
+      </c>
+      <c r="B40" t="s">
+        <v>422</v>
+      </c>
+      <c r="C40" t="s">
+        <v>423</v>
+      </c>
+      <c r="D40" t="s">
+        <v>424</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
+        <v>425</v>
+      </c>
+      <c r="G40" t="s">
+        <v>426</v>
+      </c>
+      <c r="H40" t="s">
+        <v>427</v>
+      </c>
+      <c r="I40" t="s">
+        <v>428</v>
+      </c>
+      <c r="J40" t="s">
+        <v>429</v>
+      </c>
+      <c r="K40" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>431</v>
+      </c>
+      <c r="B41" t="s">
+        <v>432</v>
+      </c>
+      <c r="C41" t="s">
+        <v>433</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" t="s">
+        <v>434</v>
+      </c>
+      <c r="G41" t="s">
+        <v>435</v>
+      </c>
+      <c r="H41" t="s">
+        <v>436</v>
+      </c>
+      <c r="I41" t="s">
+        <v>437</v>
+      </c>
+      <c r="J41" t="s">
+        <v>438</v>
+      </c>
+      <c r="K41" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" t="s">
+        <v>441</v>
+      </c>
+      <c r="C42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D42" t="s">
+        <v>443</v>
+      </c>
+      <c r="E42" t="s">
+        <v>444</v>
+      </c>
+      <c r="F42" t="s">
+        <v>445</v>
+      </c>
+      <c r="G42" t="s">
+        <v>446</v>
+      </c>
+      <c r="H42" t="s">
+        <v>447</v>
+      </c>
+      <c r="I42" t="s">
+        <v>448</v>
+      </c>
+      <c r="J42" t="s">
+        <v>449</v>
+      </c>
+      <c r="K42" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>451</v>
+      </c>
+      <c r="B43" t="s">
+        <v>452</v>
+      </c>
+      <c r="C43" t="s">
+        <v>453</v>
+      </c>
+      <c r="D43" t="s">
+        <v>454</v>
+      </c>
+      <c r="E43" t="s">
+        <v>455</v>
+      </c>
+      <c r="F43" t="s">
+        <v>456</v>
+      </c>
+      <c r="G43" t="s">
+        <v>457</v>
+      </c>
+      <c r="H43" t="s">
+        <v>458</v>
+      </c>
+      <c r="I43" t="s">
+        <v>459</v>
+      </c>
+      <c r="J43" t="s">
+        <v>460</v>
+      </c>
+      <c r="K43" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>462</v>
+      </c>
+      <c r="B44" t="s">
+        <v>463</v>
+      </c>
+      <c r="C44" t="s">
+        <v>464</v>
+      </c>
+      <c r="D44" t="s">
+        <v>465</v>
+      </c>
+      <c r="E44" t="s">
+        <v>466</v>
+      </c>
+      <c r="F44" t="s">
+        <v>467</v>
+      </c>
+      <c r="G44" t="s">
+        <v>468</v>
+      </c>
+      <c r="H44" t="s">
+        <v>469</v>
+      </c>
+      <c r="I44" t="s">
+        <v>470</v>
+      </c>
+      <c r="J44" t="s">
+        <v>471</v>
+      </c>
+      <c r="K44" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>473</v>
+      </c>
+      <c r="B45" t="s">
+        <v>474</v>
+      </c>
+      <c r="C45" t="s">
+        <v>475</v>
+      </c>
+      <c r="D45" t="s">
+        <v>537</v>
+      </c>
+      <c r="E45" t="s">
+        <v>476</v>
+      </c>
+      <c r="F45" t="s">
+        <v>477</v>
+      </c>
+      <c r="G45" t="s">
+        <v>478</v>
+      </c>
+      <c r="H45" t="s">
+        <v>479</v>
+      </c>
+      <c r="I45" t="s">
+        <v>480</v>
+      </c>
+      <c r="J45" t="s">
+        <v>481</v>
+      </c>
+      <c r="K45" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B46" t="s">
+        <v>484</v>
+      </c>
+      <c r="C46" t="s">
+        <v>485</v>
+      </c>
+      <c r="D46" t="s">
+        <v>486</v>
+      </c>
+      <c r="E46" t="s">
+        <v>487</v>
+      </c>
+      <c r="F46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G46" t="s">
+        <v>489</v>
+      </c>
+      <c r="H46" t="s">
+        <v>490</v>
+      </c>
+      <c r="I46" t="s">
+        <v>491</v>
+      </c>
+      <c r="J46" t="s">
+        <v>492</v>
+      </c>
+      <c r="K46" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>494</v>
+      </c>
+      <c r="B47" t="s">
+        <v>495</v>
+      </c>
+      <c r="C47" t="s">
+        <v>496</v>
+      </c>
+      <c r="D47" t="s">
+        <v>497</v>
+      </c>
+      <c r="E47" t="s">
+        <v>487</v>
+      </c>
+      <c r="F47" t="s">
+        <v>498</v>
+      </c>
+      <c r="G47" t="s">
+        <v>499</v>
+      </c>
+      <c r="H47" t="s">
+        <v>500</v>
+      </c>
+      <c r="I47" t="s">
+        <v>501</v>
+      </c>
+      <c r="J47" t="s">
+        <v>502</v>
+      </c>
+      <c r="K47" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>504</v>
+      </c>
+      <c r="B48" t="s">
+        <v>505</v>
+      </c>
+      <c r="C48" t="s">
+        <v>506</v>
+      </c>
+      <c r="D48" t="s">
+        <v>507</v>
+      </c>
+      <c r="E48" t="s">
+        <v>508</v>
+      </c>
+      <c r="F48" t="s">
+        <v>509</v>
+      </c>
+      <c r="G48" t="s">
+        <v>510</v>
+      </c>
+      <c r="H48" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48" t="s">
+        <v>512</v>
+      </c>
+      <c r="J48" t="s">
+        <v>513</v>
+      </c>
+      <c r="K48" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>515</v>
+      </c>
+      <c r="B49" t="s">
+        <v>516</v>
+      </c>
+      <c r="C49" t="s">
+        <v>517</v>
+      </c>
+      <c r="D49" t="s">
+        <v>518</v>
+      </c>
+      <c r="E49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" t="s">
+        <v>520</v>
+      </c>
+      <c r="G49" t="s">
+        <v>521</v>
+      </c>
+      <c r="H49" t="s">
+        <v>522</v>
+      </c>
+      <c r="I49" t="s">
+        <v>523</v>
+      </c>
+      <c r="J49" t="s">
+        <v>524</v>
+      </c>
+      <c r="K49" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>526</v>
+      </c>
+      <c r="B50" t="s">
+        <v>527</v>
+      </c>
+      <c r="C50" t="s">
+        <v>528</v>
+      </c>
+      <c r="D50" t="s">
+        <v>529</v>
+      </c>
+      <c r="E50" t="s">
+        <v>530</v>
+      </c>
+      <c r="F50" t="s">
+        <v>531</v>
+      </c>
+      <c r="G50" t="s">
+        <v>532</v>
+      </c>
+      <c r="H50" t="s">
+        <v>533</v>
+      </c>
+      <c r="I50" t="s">
+        <v>534</v>
+      </c>
+      <c r="J50" t="s">
+        <v>535</v>
+      </c>
+      <c r="K50" t="s">
+        <v>536</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>